--- a/UTHR.xlsx
+++ b/UTHR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8BC24D-869B-4C43-9E2B-EAD1E6F8F4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBB4942-934A-4478-8AC8-AF71F49FC4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48230" yWindow="640" windowWidth="23470" windowHeight="16810" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2049,7 +2049,7 @@
         <v>29</v>
       </c>
       <c r="K2" s="63">
-        <v>469</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -2078,10 +2078,10 @@
         <v>14</v>
       </c>
       <c r="K3" s="55">
-        <v>47</v>
+        <v>42.446733000000002</v>
       </c>
       <c r="L3" s="34" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K4" s="55">
         <f>K2*K3</f>
-        <v>22043</v>
+        <v>21944.960961000001</v>
       </c>
       <c r="L4" s="58"/>
     </row>
@@ -2137,10 +2137,11 @@
         <v>47</v>
       </c>
       <c r="K5" s="55">
-        <v>4335</v>
+        <f>1279.7+874+1317.4</f>
+        <v>3471.1</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -2160,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="34" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -2176,7 +2177,7 @@
       </c>
       <c r="K7" s="55">
         <f>K4-K5+K6</f>
-        <v>17708</v>
+        <v>18473.860961000002</v>
       </c>
       <c r="M7" s="58"/>
     </row>
@@ -2929,7 +2930,7 @@
         <v>125.9</v>
       </c>
       <c r="CH3" s="35">
-        <f>+CG3</f>
+        <f t="shared" ref="CH3:CH8" si="1">+CG3</f>
         <v>125.9</v>
       </c>
       <c r="CI3" s="35"/>
@@ -3019,39 +3020,39 @@
         <v>472.22999999999996</v>
       </c>
       <c r="DM3" s="16">
-        <f t="shared" ref="DM3:DU3" si="1">+DL3*0.9</f>
+        <f t="shared" ref="DM3:DU3" si="2">+DL3*0.9</f>
         <v>425.00699999999995</v>
       </c>
       <c r="DN3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>382.50629999999995</v>
       </c>
       <c r="DO3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>344.25566999999995</v>
       </c>
       <c r="DP3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>309.83010299999995</v>
       </c>
       <c r="DQ3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>278.84709269999996</v>
       </c>
       <c r="DR3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>250.96238342999996</v>
       </c>
       <c r="DS3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>225.86614508699998</v>
       </c>
       <c r="DT3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>203.27953057829998</v>
       </c>
       <c r="DU3" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>182.95157752046998</v>
       </c>
     </row>
@@ -3161,7 +3162,7 @@
         <v>336.2</v>
       </c>
       <c r="CH4" s="35">
-        <f>+CG4</f>
+        <f t="shared" si="1"/>
         <v>336.2</v>
       </c>
       <c r="CI4" s="35"/>
@@ -3192,51 +3193,51 @@
       <c r="DH4" s="16"/>
       <c r="DI4" s="12"/>
       <c r="DJ4" s="16">
-        <f t="shared" ref="DJ4:DJ12" si="2">SUM(CA4:CD4)</f>
+        <f t="shared" ref="DJ4:DJ11" si="3">SUM(CA4:CD4)</f>
         <v>1033.6000000000001</v>
       </c>
       <c r="DK4" s="16">
-        <f t="shared" ref="DK4:DK12" si="3">SUM(CE4:CH4)</f>
+        <f t="shared" ref="DK4:DK11" si="4">SUM(CE4:CH4)</f>
         <v>1290.1000000000001</v>
       </c>
       <c r="DL4" s="16">
-        <f>+DK4*1.2</f>
+        <f t="shared" ref="DL4:DQ4" si="5">+DK4*1.2</f>
         <v>1548.1200000000001</v>
       </c>
       <c r="DM4" s="16">
-        <f>+DL4*1.2</f>
+        <f t="shared" si="5"/>
         <v>1857.7440000000001</v>
       </c>
       <c r="DN4" s="16">
-        <f>+DM4*1.2</f>
+        <f t="shared" si="5"/>
         <v>2229.2928000000002</v>
       </c>
       <c r="DO4" s="16">
-        <f>+DN4*1.2</f>
+        <f t="shared" si="5"/>
         <v>2675.1513600000003</v>
       </c>
       <c r="DP4" s="16">
-        <f>+DO4*1.2</f>
+        <f t="shared" si="5"/>
         <v>3210.1816320000003</v>
       </c>
       <c r="DQ4" s="16">
-        <f>+DP4*1.2</f>
+        <f t="shared" si="5"/>
         <v>3852.2179584</v>
       </c>
       <c r="DR4" s="16">
-        <f t="shared" ref="DN4:DU4" si="4">+DQ4*0.5</f>
+        <f t="shared" ref="DR4:DU4" si="6">+DQ4*0.5</f>
         <v>1926.1089792</v>
       </c>
       <c r="DS4" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>963.05448960000001</v>
       </c>
       <c r="DT4" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>481.52724480000001</v>
       </c>
       <c r="DU4" s="16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>240.7636224</v>
       </c>
     </row>
@@ -3395,7 +3396,7 @@
         <v>141.80000000000001</v>
       </c>
       <c r="CH5" s="35">
-        <f>+CG5</f>
+        <f t="shared" si="1"/>
         <v>141.80000000000001</v>
       </c>
       <c r="CI5" s="35"/>
@@ -3459,11 +3460,11 @@
       <c r="DH5" s="16"/>
       <c r="DI5" s="12"/>
       <c r="DJ5" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>586.79999999999995</v>
       </c>
       <c r="DK5" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>601.80000000000007</v>
       </c>
       <c r="DL5" s="16">
@@ -3471,39 +3472,39 @@
         <v>541.62000000000012</v>
       </c>
       <c r="DM5" s="16">
-        <f t="shared" ref="DM5:DU5" si="5">+DL5*0.9</f>
+        <f t="shared" ref="DM5:DU5" si="7">+DL5*0.9</f>
         <v>487.45800000000014</v>
       </c>
       <c r="DN5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>438.71220000000011</v>
       </c>
       <c r="DO5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>394.84098000000012</v>
       </c>
       <c r="DP5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>355.3568820000001</v>
       </c>
       <c r="DQ5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>319.82119380000012</v>
       </c>
       <c r="DR5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>287.83907442000009</v>
       </c>
       <c r="DS5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>259.0551669780001</v>
       </c>
       <c r="DT5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>233.14965028020009</v>
       </c>
       <c r="DU5" s="16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>209.83468525218009</v>
       </c>
     </row>
@@ -3659,7 +3660,7 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="CH6" s="35">
-        <f>+CG6</f>
+        <f t="shared" si="1"/>
         <v>9.6999999999999993</v>
       </c>
       <c r="CI6" s="35"/>
@@ -3698,78 +3699,78 @@
         <v>84.975033000000039</v>
       </c>
       <c r="DA6" s="35">
-        <f t="shared" ref="DA6:DF6" si="6">+CZ6*0.5</f>
+        <f t="shared" ref="DA6:DF6" si="8">+CZ6*0.5</f>
         <v>42.487516500000019</v>
       </c>
       <c r="DB6" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>21.24375825000001</v>
       </c>
       <c r="DC6" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>10.621879125000005</v>
       </c>
       <c r="DD6" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>5.3109395625000024</v>
       </c>
       <c r="DE6" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.6554697812500012</v>
       </c>
       <c r="DF6" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.3277348906250006</v>
       </c>
       <c r="DG6" s="16"/>
       <c r="DH6" s="16"/>
       <c r="DI6" s="12"/>
       <c r="DJ6" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>23.8</v>
       </c>
       <c r="DK6" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>31.9</v>
       </c>
       <c r="DL6" s="16">
-        <f t="shared" ref="DL6:DU6" si="7">+DK6*0.9</f>
+        <f t="shared" ref="DL6:DU6" si="9">+DK6*0.9</f>
         <v>28.71</v>
       </c>
       <c r="DM6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>25.839000000000002</v>
       </c>
       <c r="DN6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>23.255100000000002</v>
       </c>
       <c r="DO6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>20.929590000000001</v>
       </c>
       <c r="DP6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>18.836631000000001</v>
       </c>
       <c r="DQ6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16.952967900000001</v>
       </c>
       <c r="DR6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15.25767111</v>
       </c>
       <c r="DS6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>13.731903999</v>
       </c>
       <c r="DT6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>12.3587135991</v>
       </c>
       <c r="DU6" s="16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>11.12284223919</v>
       </c>
     </row>
@@ -3905,7 +3906,7 @@
         <v>131.1</v>
       </c>
       <c r="CH7" s="35">
-        <f>+CG7</f>
+        <f t="shared" si="1"/>
         <v>131.1</v>
       </c>
       <c r="CI7" s="35"/>
@@ -3936,51 +3937,51 @@
       <c r="DH7" s="16"/>
       <c r="DI7" s="12"/>
       <c r="DJ7" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>434.3</v>
       </c>
       <c r="DK7" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>506.80000000000007</v>
       </c>
       <c r="DL7" s="16">
-        <f t="shared" ref="DL7:DU8" si="8">+DK7*0.9</f>
+        <f t="shared" ref="DL7:DU7" si="10">+DK7*0.9</f>
         <v>456.12000000000006</v>
       </c>
       <c r="DM7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>410.50800000000004</v>
       </c>
       <c r="DN7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>369.45720000000006</v>
       </c>
       <c r="DO7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>332.51148000000006</v>
       </c>
       <c r="DP7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>299.26033200000006</v>
       </c>
       <c r="DQ7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>269.33429880000006</v>
       </c>
       <c r="DR7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>242.40086892000005</v>
       </c>
       <c r="DS7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>218.16078202800006</v>
       </c>
       <c r="DT7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>196.34470382520004</v>
       </c>
       <c r="DU7" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>176.71023344268005</v>
       </c>
     </row>
@@ -4116,7 +4117,7 @@
         <v>47.9</v>
       </c>
       <c r="CH8" s="35">
-        <f>+CG8</f>
+        <f t="shared" si="1"/>
         <v>47.9</v>
       </c>
       <c r="CI8" s="35"/>
@@ -4147,11 +4148,11 @@
       <c r="DH8" s="16"/>
       <c r="DI8" s="12"/>
       <c r="DJ8" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>238.7</v>
       </c>
       <c r="DK8" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212.4</v>
       </c>
       <c r="DL8" s="16">
@@ -4159,39 +4160,39 @@
         <v>201.78</v>
       </c>
       <c r="DM8" s="16">
-        <f t="shared" ref="DM8:DU8" si="9">+DL8*0.95</f>
+        <f t="shared" ref="DM8:DU8" si="11">+DL8*0.95</f>
         <v>191.691</v>
       </c>
       <c r="DN8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>182.10645</v>
       </c>
       <c r="DO8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>173.0011275</v>
       </c>
       <c r="DP8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>164.35107112499998</v>
       </c>
       <c r="DQ8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>156.13351756874997</v>
       </c>
       <c r="DR8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>148.32684169031245</v>
       </c>
       <c r="DS8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>140.91049960579682</v>
       </c>
       <c r="DT8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>133.86497462550696</v>
       </c>
       <c r="DU8" s="16">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>127.1717258942316</v>
       </c>
     </row>
@@ -4412,51 +4413,51 @@
       <c r="DH9" s="16"/>
       <c r="DI9" s="12"/>
       <c r="DJ9" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DK9" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="DK9" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="DL9" s="16">
-        <f t="shared" ref="DL9:DU9" si="10">+DK9*0.95</f>
+        <f t="shared" ref="DL9:DU9" si="12">+DK9*0.95</f>
         <v>0</v>
       </c>
       <c r="DM9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DN9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DO9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DP9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DQ9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DR9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DS9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DT9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="DU9" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -4696,51 +4697,51 @@
       <c r="DH10" s="16"/>
       <c r="DI10" s="12"/>
       <c r="DJ10" s="16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22.1</v>
       </c>
       <c r="DK10" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24.299999999999997</v>
       </c>
       <c r="DL10" s="16">
-        <f t="shared" ref="DL10:DU10" si="11">+DK10*0.95</f>
+        <f t="shared" ref="DL10:DU10" si="13">+DK10*0.95</f>
         <v>23.084999999999997</v>
       </c>
       <c r="DM10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>21.930749999999996</v>
       </c>
       <c r="DN10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>20.834212499999996</v>
       </c>
       <c r="DO10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>19.792501874999996</v>
       </c>
       <c r="DP10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>18.802876781249996</v>
       </c>
       <c r="DQ10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>17.862732942187495</v>
       </c>
       <c r="DR10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>16.969596295078119</v>
       </c>
       <c r="DS10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>16.121116480324211</v>
       </c>
       <c r="DT10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>15.315060656308001</v>
       </c>
       <c r="DU10" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>14.5493076234926</v>
       </c>
     </row>
@@ -4894,51 +4895,51 @@
       <c r="DH11" s="16"/>
       <c r="DI11" s="12"/>
       <c r="DJ11" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DK11" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="DK11" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="DL11" s="16">
-        <f t="shared" ref="DL11:DU11" si="12">+DK11*0.95</f>
+        <f t="shared" ref="DL11:DU11" si="14">+DK11*0.95</f>
         <v>0</v>
       </c>
       <c r="DM11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DN11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DO11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DP11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DQ11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DR11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DS11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DT11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="DU11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -4955,83 +4956,83 @@
         <v>30.057000000000002</v>
       </c>
       <c r="E12" s="20">
-        <f t="shared" ref="E12:L12" si="13">SUM(E3:E11)</f>
+        <f t="shared" ref="E12:L12" si="15">SUM(E3:E11)</f>
         <v>33.01</v>
       </c>
       <c r="F12" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>29.640999999999998</v>
       </c>
       <c r="G12" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>33.163999999999994</v>
       </c>
       <c r="H12" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>40.245000000000005</v>
       </c>
       <c r="I12" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>40.397000000000006</v>
       </c>
       <c r="J12" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>45.826000000000001</v>
       </c>
       <c r="K12" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>40.169000000000004</v>
       </c>
       <c r="L12" s="20">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>51.831000000000003</v>
       </c>
       <c r="M12" s="20">
-        <f t="shared" ref="M12:T12" si="14">SUM(M3:M11)</f>
+        <f t="shared" ref="M12:T12" si="16">SUM(M3:M11)</f>
         <v>59.045000000000002</v>
       </c>
       <c r="N12" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>59.897999999999996</v>
       </c>
       <c r="O12" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>62.046999999999997</v>
       </c>
       <c r="P12" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>68.555999999999997</v>
       </c>
       <c r="Q12" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>75.031999999999996</v>
       </c>
       <c r="R12" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>75.862000000000009</v>
       </c>
       <c r="S12" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>79.73</v>
       </c>
       <c r="T12" s="20">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>83.97999999999999</v>
       </c>
       <c r="U12" s="20">
-        <f t="shared" ref="U12:AD12" si="15">SUM(U3:U11)</f>
+        <f t="shared" ref="U12:AD12" si="17">SUM(U3:U11)</f>
         <v>97.215000000000003</v>
       </c>
       <c r="V12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>108.92300000000002</v>
       </c>
       <c r="W12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>128.88000000000002</v>
       </c>
       <c r="X12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>137.49100000000004</v>
       </c>
       <c r="Y12" s="20">
@@ -5039,23 +5040,23 @@
         <v>170.98299999999998</v>
       </c>
       <c r="Z12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>166.47700000000003</v>
       </c>
       <c r="AA12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>167</v>
       </c>
       <c r="AB12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>183.751</v>
       </c>
       <c r="AC12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>175.89400000000001</v>
       </c>
       <c r="AD12" s="20">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>176.89400000000001</v>
       </c>
       <c r="AE12" s="20"/>
@@ -5092,27 +5093,27 @@
       <c r="BJ12" s="36"/>
       <c r="BK12" s="36"/>
       <c r="BL12" s="36">
-        <f t="shared" ref="BL12:BQ12" si="16">SUM(BL3:BL11)</f>
+        <f t="shared" ref="BL12:BQ12" si="18">SUM(BL3:BL11)</f>
         <v>362</v>
       </c>
       <c r="BM12" s="36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>380.1</v>
       </c>
       <c r="BN12" s="36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>384.90000000000003</v>
       </c>
       <c r="BO12" s="36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>379.1</v>
       </c>
       <c r="BP12" s="36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>446.50000000000006</v>
       </c>
       <c r="BQ12" s="36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>444.70000000000005</v>
       </c>
       <c r="BR12" s="36">
@@ -5132,71 +5133,71 @@
         <v>516</v>
       </c>
       <c r="BV12" s="36">
-        <f t="shared" ref="BV12:CL12" si="17">SUM(BV3:BV11)</f>
+        <f t="shared" ref="BV12:CL12" si="19">SUM(BV3:BV11)</f>
         <v>491.5</v>
       </c>
       <c r="BW12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>506.90000000000003</v>
       </c>
       <c r="BX12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>596.49999999999989</v>
       </c>
       <c r="BY12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>609.4</v>
       </c>
       <c r="BZ12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>614.69999999999993</v>
       </c>
       <c r="CA12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>677.7</v>
       </c>
       <c r="CB12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>714.90000000000009</v>
       </c>
       <c r="CC12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>748.90000000000009</v>
       </c>
       <c r="CD12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>735.9</v>
       </c>
       <c r="CE12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>794.40000000000009</v>
       </c>
       <c r="CF12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>798.59999999999991</v>
       </c>
       <c r="CG12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>799.50000000000011</v>
       </c>
       <c r="CH12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>799.50000000000011</v>
       </c>
       <c r="CI12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="CJ12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="CK12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="CL12" s="36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="CM12" s="36"/>
@@ -5231,31 +5232,31 @@
         <v>603.83100000000002</v>
       </c>
       <c r="CW12" s="36">
-        <f t="shared" ref="CW12:DC12" si="18">SUM(CW3:CW10)</f>
+        <f t="shared" ref="CW12:DC12" si="20">SUM(CW3:CW10)</f>
         <v>703.53899999999999</v>
       </c>
       <c r="CX12" s="36">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>776.25144999999998</v>
       </c>
       <c r="CY12" s="36">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>791.93203000000005</v>
       </c>
       <c r="CZ12" s="36">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>824.65703300000007</v>
       </c>
       <c r="DA12" s="36">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>782.16951649999999</v>
       </c>
       <c r="DB12" s="36">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>760.92575825000006</v>
       </c>
       <c r="DC12" s="20">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>504.86747912500005</v>
       </c>
       <c r="DD12" s="20">
@@ -5274,7 +5275,7 @@
       <c r="DH12" s="20"/>
       <c r="DI12" s="85"/>
       <c r="DJ12" s="20">
-        <f t="shared" ref="DJ12:DK12" si="19">SUM(DJ3:DJ10)</f>
+        <f t="shared" ref="DJ12" si="21">SUM(DJ3:DJ10)</f>
         <v>2877.4</v>
       </c>
       <c r="DK12" s="20">
@@ -5282,43 +5283,43 @@
         <v>3192.0000000000009</v>
       </c>
       <c r="DL12" s="20">
-        <f t="shared" ref="DL12:DU12" si="20">SUM(DL3:DL10)</f>
+        <f t="shared" ref="DL12:DU12" si="22">SUM(DL3:DL10)</f>
         <v>3271.6650000000004</v>
       </c>
       <c r="DM12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3420.1777500000003</v>
       </c>
       <c r="DN12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3646.1642625000004</v>
       </c>
       <c r="DO12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>3960.4827093750009</v>
       </c>
       <c r="DP12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4376.6195279062504</v>
       </c>
       <c r="DQ12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>4911.1697621109388</v>
       </c>
       <c r="DR12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2887.8654150653906</v>
       </c>
       <c r="DS12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1836.9001037781213</v>
       </c>
       <c r="DT12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1275.8398783646153</v>
       </c>
       <c r="DU12" s="20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>963.10399437224441</v>
       </c>
     </row>
@@ -5567,7 +5568,7 @@
         <v>30.065000000000055</v>
       </c>
       <c r="CU13" s="35">
-        <f t="shared" ref="CU13:DC13" si="21">CU12-CU14</f>
+        <f t="shared" ref="CU13:DC13" si="23">CU12-CU14</f>
         <v>42.908000000000015</v>
       </c>
       <c r="CV13" s="35">
@@ -5579,27 +5580,27 @@
         <v>84.424679999999995</v>
       </c>
       <c r="CX13" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>93.150173999999993</v>
       </c>
       <c r="CY13" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>95.031843600000002</v>
       </c>
       <c r="CZ13" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>98.958843959999967</v>
       </c>
       <c r="DA13" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>93.860341980000044</v>
       </c>
       <c r="DB13" s="35">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>91.311090990000025</v>
       </c>
       <c r="DC13" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>60.58409749499998</v>
       </c>
       <c r="DD13" s="16">
@@ -5612,11 +5613,11 @@
       <c r="DH13" s="16"/>
       <c r="DI13" s="12"/>
       <c r="DJ13" s="16">
-        <f t="shared" ref="DJ13" si="22">SUM(CA13:CD13)</f>
+        <f t="shared" ref="DJ13" si="24">SUM(CA13:CD13)</f>
         <v>308.59999999999997</v>
       </c>
       <c r="DK13" s="16">
-        <f t="shared" ref="DK13" si="23">SUM(CE13:CH13)</f>
+        <f t="shared" ref="DK13" si="25">SUM(CE13:CH13)</f>
         <v>382.13500000000005</v>
       </c>
       <c r="DL13" s="16">
@@ -5624,39 +5625,39 @@
         <v>327.16649999999981</v>
       </c>
       <c r="DM13" s="16">
-        <f t="shared" ref="DM13:DU13" si="24">+DM12-DM14</f>
+        <f t="shared" ref="DM13:DU13" si="26">+DM12-DM14</f>
         <v>342.0177749999998</v>
       </c>
       <c r="DN13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>364.61642625000013</v>
       </c>
       <c r="DO13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>396.04827093750009</v>
       </c>
       <c r="DP13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>437.66195279062504</v>
       </c>
       <c r="DQ13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>491.11697621109397</v>
       </c>
       <c r="DR13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>288.78654150653892</v>
       </c>
       <c r="DS13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>183.69001037781209</v>
       </c>
       <c r="DT13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>127.58398783646157</v>
       </c>
       <c r="DU13" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>96.310399437224419</v>
       </c>
     </row>
@@ -5677,67 +5678,67 @@
         <v>29.577999999999999</v>
       </c>
       <c r="F14" s="16">
-        <f t="shared" ref="F14:L14" si="25">F12-F13</f>
+        <f t="shared" ref="F14:L14" si="27">F12-F13</f>
         <v>26.488</v>
       </c>
       <c r="G14" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>29.286999999999995</v>
       </c>
       <c r="H14" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>36.001000000000005</v>
       </c>
       <c r="I14" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>36.243000000000009</v>
       </c>
       <c r="J14" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>41.073</v>
       </c>
       <c r="K14" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>35.773000000000003</v>
       </c>
       <c r="L14" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>46.489000000000004</v>
       </c>
       <c r="M14" s="16">
-        <f t="shared" ref="M14:U14" si="26">M12-M13</f>
+        <f t="shared" ref="M14:U14" si="28">M12-M13</f>
         <v>52.879000000000005</v>
       </c>
       <c r="N14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>53.540999999999997</v>
       </c>
       <c r="O14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>55.160999999999994</v>
       </c>
       <c r="P14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>61.223999999999997</v>
       </c>
       <c r="Q14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>67.290999999999997</v>
       </c>
       <c r="R14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>67.756000000000014</v>
       </c>
       <c r="S14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>70.744</v>
       </c>
       <c r="T14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>76.298999999999992</v>
       </c>
       <c r="U14" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>84.460000000000008</v>
       </c>
       <c r="V14" s="16">
@@ -5753,27 +5754,27 @@
         <v>120.80700000000004</v>
       </c>
       <c r="Y14" s="16">
-        <f t="shared" ref="Y14:AD14" si="27">Y12-Y13</f>
+        <f t="shared" ref="Y14:AD14" si="29">Y12-Y13</f>
         <v>149.26099999999997</v>
       </c>
       <c r="Z14" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>147.94100000000003</v>
       </c>
       <c r="AA14" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>146.96</v>
       </c>
       <c r="AB14" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>161.70088000000001</v>
       </c>
       <c r="AC14" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>154.78672</v>
       </c>
       <c r="AD14" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>155.66672</v>
       </c>
       <c r="AE14" s="16"/>
@@ -5810,31 +5811,31 @@
       <c r="BJ14" s="35"/>
       <c r="BK14" s="35"/>
       <c r="BL14" s="35">
-        <f t="shared" ref="BL14:BR14" si="28">BL12-BL13</f>
+        <f t="shared" ref="BL14:BR14" si="30">BL12-BL13</f>
         <v>336.1</v>
       </c>
       <c r="BM14" s="35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>356.1</v>
       </c>
       <c r="BN14" s="35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>350.1</v>
       </c>
       <c r="BO14" s="35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>356.1</v>
       </c>
       <c r="BP14" s="35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>409.30000000000007</v>
       </c>
       <c r="BQ14" s="35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>417.00000000000006</v>
       </c>
       <c r="BR14" s="35">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>380.6</v>
       </c>
       <c r="BS14" s="35">
@@ -5846,35 +5847,35 @@
         <v>437.2</v>
       </c>
       <c r="BU14" s="35">
-        <f t="shared" ref="BU14:CB14" si="29">+BU12-BU13</f>
+        <f t="shared" ref="BU14:CB14" si="31">+BU12-BU13</f>
         <v>478.8</v>
       </c>
       <c r="BV14" s="35">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>432.7</v>
       </c>
       <c r="BW14" s="35">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>454.6</v>
       </c>
       <c r="BX14" s="35">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>532.39999999999986</v>
       </c>
       <c r="BY14" s="35">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>539.29999999999995</v>
       </c>
       <c r="BZ14" s="35">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>543.69999999999993</v>
       </c>
       <c r="CA14" s="35">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>604.80000000000007</v>
       </c>
       <c r="CB14" s="35">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>637.10000000000014</v>
       </c>
       <c r="CC14" s="35">
@@ -5941,27 +5942,27 @@
         <v>619.11432000000002</v>
       </c>
       <c r="CX14" s="35">
-        <f t="shared" ref="CX14:DC14" si="30">CX12*CX34</f>
+        <f t="shared" ref="CX14:DC14" si="32">CX12*CX34</f>
         <v>683.10127599999998</v>
       </c>
       <c r="CY14" s="35">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>696.90018640000005</v>
       </c>
       <c r="CZ14" s="35">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>725.6981890400001</v>
       </c>
       <c r="DA14" s="35">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>688.30917451999994</v>
       </c>
       <c r="DB14" s="35">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>669.61466726000003</v>
       </c>
       <c r="DC14" s="16">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>444.28338163000006</v>
       </c>
       <c r="DD14" s="16">
@@ -5986,39 +5987,39 @@
         <v>2944.4985000000006</v>
       </c>
       <c r="DM14" s="16">
-        <f t="shared" ref="DM14:DU14" si="31">+DM12*0.9</f>
+        <f t="shared" ref="DM14:DU14" si="33">+DM12*0.9</f>
         <v>3078.1599750000005</v>
       </c>
       <c r="DN14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3281.5478362500003</v>
       </c>
       <c r="DO14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3564.4344384375008</v>
       </c>
       <c r="DP14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>3938.9575751156253</v>
       </c>
       <c r="DQ14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>4420.0527858998448</v>
       </c>
       <c r="DR14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2599.0788735588517</v>
       </c>
       <c r="DS14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1653.2100934003092</v>
       </c>
       <c r="DT14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1148.2558905281537</v>
       </c>
       <c r="DU14" s="16">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>866.79359493502</v>
       </c>
     </row>
@@ -6294,11 +6295,11 @@
       <c r="DH15" s="16"/>
       <c r="DI15" s="12"/>
       <c r="DJ15" s="16">
-        <f t="shared" ref="DJ15:DJ16" si="32">SUM(CA15:CD15)</f>
+        <f t="shared" ref="DJ15:DJ16" si="34">SUM(CA15:CD15)</f>
         <v>684.5</v>
       </c>
       <c r="DK15" s="16">
-        <f t="shared" ref="DK15:DK16" si="33">SUM(CE15:CH15)</f>
+        <f t="shared" ref="DK15:DK16" si="35">SUM(CE15:CH15)</f>
         <v>612.20000000000005</v>
       </c>
       <c r="DL15" s="16">
@@ -6306,39 +6307,39 @@
         <v>654.33300000000008</v>
       </c>
       <c r="DM15" s="16">
-        <f t="shared" ref="DM15:DU15" si="34">+DM12*0.2</f>
+        <f t="shared" ref="DM15:DU15" si="36">+DM12*0.2</f>
         <v>684.03555000000006</v>
       </c>
       <c r="DN15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>729.23285250000015</v>
       </c>
       <c r="DO15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>792.09654187500018</v>
       </c>
       <c r="DP15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>875.32390558125007</v>
       </c>
       <c r="DQ15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>982.23395242218783</v>
       </c>
       <c r="DR15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>577.57308301307819</v>
       </c>
       <c r="DS15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>367.38002075562429</v>
       </c>
       <c r="DT15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>255.16797567292306</v>
       </c>
       <c r="DU15" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>192.62079887444889</v>
       </c>
     </row>
@@ -6589,11 +6590,11 @@
       <c r="DH16" s="16"/>
       <c r="DI16" s="12"/>
       <c r="DJ16" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>474.29999999999995</v>
       </c>
       <c r="DK16" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>506.20000000000005</v>
       </c>
       <c r="DL16" s="12"/>
@@ -6752,87 +6753,87 @@
         <v>124</v>
       </c>
       <c r="C18" s="16">
-        <f t="shared" ref="C18:J18" si="35">C16+C15</f>
+        <f t="shared" ref="C18:J18" si="37">C16+C15</f>
         <v>13.813000000000001</v>
       </c>
       <c r="D18" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>15.719000000000001</v>
       </c>
       <c r="E18" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>15.042999999999999</v>
       </c>
       <c r="F18" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>16.132999999999999</v>
       </c>
       <c r="G18" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>26.803000000000001</v>
       </c>
       <c r="H18" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>24.484999999999999</v>
       </c>
       <c r="I18" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>24.810000000000002</v>
       </c>
       <c r="J18" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>37.524000000000001</v>
       </c>
       <c r="K18" s="16">
-        <f t="shared" ref="K18:S18" si="36">SUM(K15:K16)</f>
+        <f t="shared" ref="K18:S18" si="38">SUM(K15:K16)</f>
         <v>32.265000000000001</v>
       </c>
       <c r="L18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>38.444000000000003</v>
       </c>
       <c r="M18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>38.722000000000001</v>
       </c>
       <c r="N18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>61.936</v>
       </c>
       <c r="O18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>40.406999999999996</v>
       </c>
       <c r="P18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>34.587999999999994</v>
       </c>
       <c r="Q18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>49.231000000000002</v>
       </c>
       <c r="R18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>48.616</v>
       </c>
       <c r="S18" s="16">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>50.177</v>
       </c>
       <c r="T18" s="16">
-        <f t="shared" ref="T18:AD18" si="37">SUM(T15:T16)</f>
+        <f t="shared" ref="T18:AD18" si="39">SUM(T15:T16)</f>
         <v>43.722000000000008</v>
       </c>
       <c r="U18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>72.722999999999999</v>
       </c>
       <c r="V18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>97.608999999999995</v>
       </c>
       <c r="W18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>81.748000000000005</v>
       </c>
       <c r="X18" s="16">
@@ -6840,15 +6841,15 @@
         <v>59.980000000000004</v>
       </c>
       <c r="Y18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>87.38</v>
       </c>
       <c r="Z18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>137.25300000000001</v>
       </c>
       <c r="AA18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>110</v>
       </c>
       <c r="AB18" s="16">
@@ -6856,11 +6857,11 @@
         <v>94.34</v>
       </c>
       <c r="AC18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>120</v>
       </c>
       <c r="AD18" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>130</v>
       </c>
       <c r="AE18" s="16"/>
@@ -6897,31 +6898,31 @@
       <c r="BJ18" s="35"/>
       <c r="BK18" s="35"/>
       <c r="BL18" s="35">
-        <f t="shared" ref="BL18" si="38">BL16+BL15</f>
+        <f t="shared" ref="BL18" si="40">BL16+BL15</f>
         <v>195.60000000000002</v>
       </c>
       <c r="BM18" s="35">
-        <f t="shared" ref="BM18" si="39">BM16+BM15</f>
+        <f t="shared" ref="BM18" si="41">BM16+BM15</f>
         <v>135</v>
       </c>
       <c r="BN18" s="35">
-        <f t="shared" ref="BN18" si="40">BN16+BN15</f>
+        <f t="shared" ref="BN18" si="42">BN16+BN15</f>
         <v>212.09999999999997</v>
       </c>
       <c r="BO18" s="35">
-        <f t="shared" ref="BO18:BR18" si="41">BO16+BO15</f>
+        <f t="shared" ref="BO18:BR18" si="43">BO16+BO15</f>
         <v>197</v>
       </c>
       <c r="BP18" s="35">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>187.1</v>
       </c>
       <c r="BQ18" s="35">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>188.3</v>
       </c>
       <c r="BR18" s="35">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>175.3</v>
       </c>
       <c r="BS18" s="35">
@@ -6929,55 +6930,55 @@
         <v>148</v>
       </c>
       <c r="BT18" s="35">
-        <f t="shared" ref="BT18:BU18" si="42">BT16+BT15</f>
+        <f t="shared" ref="BT18:BU18" si="44">BT16+BT15</f>
         <v>235.4</v>
       </c>
       <c r="BU18" s="35">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>164.5</v>
       </c>
       <c r="BV18" s="35">
-        <f t="shared" ref="BV18:BZ18" si="43">BV16+BV15</f>
+        <f t="shared" ref="BV18:BZ18" si="45">BV16+BV15</f>
         <v>206.2</v>
       </c>
       <c r="BW18" s="35">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>170.2</v>
       </c>
       <c r="BX18" s="35">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>219</v>
       </c>
       <c r="BY18" s="35">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>212.3</v>
       </c>
       <c r="BZ18" s="35">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>283.60000000000002</v>
       </c>
       <c r="CA18" s="35">
-        <f t="shared" ref="CA18:CB18" si="44">CA16+CA15</f>
+        <f t="shared" ref="CA18:CB18" si="46">CA16+CA15</f>
         <v>248.5</v>
       </c>
       <c r="CB18" s="35">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>317.2</v>
       </c>
       <c r="CC18" s="35">
-        <f t="shared" ref="CC18:CH18" si="45">CC16+CC15</f>
+        <f t="shared" ref="CC18:CF18" si="47">CC16+CC15</f>
         <v>322.7</v>
       </c>
       <c r="CD18" s="35">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>270.39999999999998</v>
       </c>
       <c r="CE18" s="35">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>288.2</v>
       </c>
       <c r="CF18" s="35">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>288</v>
       </c>
       <c r="CG18" s="35">
@@ -6996,15 +6997,15 @@
       <c r="CN18" s="35"/>
       <c r="CO18" s="48"/>
       <c r="CP18" s="35">
-        <f t="shared" ref="CP18:CU18" si="46">SUM(CP15:CP16)</f>
+        <f t="shared" ref="CP18:CU18" si="48">SUM(CP15:CP16)</f>
         <v>52.131</v>
       </c>
       <c r="CQ18" s="35">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>60.707000000000001</v>
       </c>
       <c r="CR18" s="35">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>113.622</v>
       </c>
       <c r="CS18" s="35">
@@ -7016,39 +7017,39 @@
         <v>172.84199999999998</v>
       </c>
       <c r="CU18" s="35">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>264.23099999999999</v>
       </c>
       <c r="CV18" s="35">
-        <f t="shared" ref="CV18:DC18" si="47">SUM(CV15:CV16)</f>
+        <f t="shared" ref="CV18:DC18" si="49">SUM(CV15:CV16)</f>
         <v>366.36099999999999</v>
       </c>
       <c r="CW18" s="35">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>454.34000000000003</v>
       </c>
       <c r="CX18" s="35">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>186.34</v>
       </c>
       <c r="CY18" s="35">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>186.34</v>
       </c>
       <c r="CZ18" s="35">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>161.34</v>
       </c>
       <c r="DA18" s="35">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>136.34</v>
       </c>
       <c r="DB18" s="35">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>111.34</v>
       </c>
       <c r="DC18" s="16">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>86.34</v>
       </c>
       <c r="DD18" s="16">
@@ -7069,43 +7070,43 @@
         <v>1118.4000000000001</v>
       </c>
       <c r="DL18" s="16">
-        <f t="shared" ref="DL18:DU18" si="48">SUM(DL15:DL16)</f>
+        <f t="shared" ref="DL18:DU18" si="50">SUM(DL15:DL16)</f>
         <v>654.33300000000008</v>
       </c>
       <c r="DM18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>684.03555000000006</v>
       </c>
       <c r="DN18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>729.23285250000015</v>
       </c>
       <c r="DO18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>792.09654187500018</v>
       </c>
       <c r="DP18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>875.32390558125007</v>
       </c>
       <c r="DQ18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>982.23395242218783</v>
       </c>
       <c r="DR18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>577.57308301307819</v>
       </c>
       <c r="DS18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>367.38002075562429</v>
       </c>
       <c r="DT18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>255.16797567292306</v>
       </c>
       <c r="DU18" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>192.62079887444889</v>
       </c>
     </row>
@@ -7114,115 +7115,115 @@
         <v>125</v>
       </c>
       <c r="C19" s="20">
-        <f t="shared" ref="C19:N19" si="49">C14-C18</f>
+        <f t="shared" ref="C19:N19" si="51">C14-C18</f>
         <v>6.8389999999999969</v>
       </c>
       <c r="D19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.163</v>
       </c>
       <c r="E19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>14.535</v>
       </c>
       <c r="F19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>10.355</v>
       </c>
       <c r="G19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>2.4839999999999947</v>
       </c>
       <c r="H19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.516000000000005</v>
       </c>
       <c r="I19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.433000000000007</v>
       </c>
       <c r="J19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>3.5489999999999995</v>
       </c>
       <c r="K19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>3.5080000000000027</v>
       </c>
       <c r="L19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>8.0450000000000017</v>
       </c>
       <c r="M19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>14.157000000000004</v>
       </c>
       <c r="N19" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-8.3950000000000031</v>
       </c>
       <c r="O19" s="20">
-        <f t="shared" ref="O19:V19" si="50">O14-O18</f>
+        <f t="shared" ref="O19:V19" si="52">O14-O18</f>
         <v>14.753999999999998</v>
       </c>
       <c r="P19" s="20">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>26.636000000000003</v>
       </c>
       <c r="Q19" s="20">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>18.059999999999995</v>
       </c>
       <c r="R19" s="20">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>19.140000000000015</v>
       </c>
       <c r="S19" s="20">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>20.567</v>
       </c>
       <c r="T19" s="20">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>32.576999999999984</v>
       </c>
       <c r="U19" s="20">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>11.737000000000009</v>
       </c>
       <c r="V19" s="20">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>-2.1719999999999828</v>
       </c>
       <c r="W19" s="20">
-        <f t="shared" ref="W19:AD19" si="51">W14-W18</f>
+        <f t="shared" ref="W19:AD19" si="53">W14-W18</f>
         <v>32.246000000000024</v>
       </c>
       <c r="X19" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>60.827000000000041</v>
       </c>
       <c r="Y19" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>61.880999999999972</v>
       </c>
       <c r="Z19" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>10.688000000000017</v>
       </c>
       <c r="AA19" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>36.960000000000008</v>
       </c>
       <c r="AB19" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>67.360880000000009</v>
       </c>
       <c r="AC19" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>34.786720000000003</v>
       </c>
       <c r="AD19" s="20">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>25.666719999999998</v>
       </c>
       <c r="AE19" s="20"/>
@@ -7259,31 +7260,31 @@
       <c r="BJ19" s="36"/>
       <c r="BK19" s="36"/>
       <c r="BL19" s="36">
-        <f t="shared" ref="BL19" si="52">BL14-BL18</f>
+        <f t="shared" ref="BL19" si="54">BL14-BL18</f>
         <v>140.5</v>
       </c>
       <c r="BM19" s="36">
-        <f t="shared" ref="BM19" si="53">BM14-BM18</f>
+        <f t="shared" ref="BM19" si="55">BM14-BM18</f>
         <v>221.10000000000002</v>
       </c>
       <c r="BN19" s="36">
-        <f t="shared" ref="BN19" si="54">BN14-BN18</f>
+        <f t="shared" ref="BN19" si="56">BN14-BN18</f>
         <v>138.00000000000006</v>
       </c>
       <c r="BO19" s="36">
-        <f t="shared" ref="BO19:BR19" si="55">BO14-BO18</f>
+        <f t="shared" ref="BO19:BR19" si="57">BO14-BO18</f>
         <v>159.10000000000002</v>
       </c>
       <c r="BP19" s="36">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>222.20000000000007</v>
       </c>
       <c r="BQ19" s="36">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>228.70000000000005</v>
       </c>
       <c r="BR19" s="36">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>205.3</v>
       </c>
       <c r="BS19" s="36">
@@ -7291,63 +7292,63 @@
         <v>288.00000000000006</v>
       </c>
       <c r="BT19" s="36">
-        <f t="shared" ref="BT19:BU19" si="56">BT14-BT18</f>
+        <f t="shared" ref="BT19:BU19" si="58">BT14-BT18</f>
         <v>201.79999999999998</v>
       </c>
       <c r="BU19" s="36">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>314.3</v>
       </c>
       <c r="BV19" s="36">
-        <f t="shared" ref="BV19" si="57">BV14-BV18</f>
+        <f t="shared" ref="BV19" si="59">BV14-BV18</f>
         <v>226.5</v>
       </c>
       <c r="BW19" s="36">
-        <f t="shared" ref="BW19" si="58">BW14-BW18</f>
+        <f t="shared" ref="BW19" si="60">BW14-BW18</f>
         <v>284.40000000000003</v>
       </c>
       <c r="BX19" s="36">
-        <f t="shared" ref="BX19" si="59">BX14-BX18</f>
+        <f t="shared" ref="BX19" si="61">BX14-BX18</f>
         <v>313.39999999999986</v>
       </c>
       <c r="BY19" s="36">
-        <f t="shared" ref="BY19" si="60">BY14-BY18</f>
+        <f t="shared" ref="BY19" si="62">BY14-BY18</f>
         <v>326.99999999999994</v>
       </c>
       <c r="BZ19" s="36">
-        <f t="shared" ref="BZ19:CB19" si="61">BZ14-BZ18</f>
+        <f t="shared" ref="BZ19:CB19" si="63">BZ14-BZ18</f>
         <v>260.09999999999991</v>
       </c>
       <c r="CA19" s="36">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>356.30000000000007</v>
       </c>
       <c r="CB19" s="36">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>319.90000000000015</v>
       </c>
       <c r="CC19" s="36">
-        <f t="shared" ref="CC19:CH19" si="62">CC14-CC18</f>
+        <f t="shared" ref="CC19:CH19" si="64">CC14-CC18</f>
         <v>343.10000000000008</v>
       </c>
       <c r="CD19" s="36">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>390.70000000000005</v>
       </c>
       <c r="CE19" s="36">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>414.60000000000008</v>
       </c>
       <c r="CF19" s="36">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>423.99999999999989</v>
       </c>
       <c r="CG19" s="36">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>428.40000000000009</v>
       </c>
       <c r="CH19" s="36">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>424.46500000000003</v>
       </c>
       <c r="CI19" s="36"/>
@@ -7378,39 +7379,39 @@
         <v>78.590000000000032</v>
       </c>
       <c r="CU19" s="36">
-        <f t="shared" ref="CU19:DC19" si="63">(CU14-CU18)</f>
+        <f t="shared" ref="CU19:DC19" si="65">(CU14-CU18)</f>
         <v>62.70900000000006</v>
       </c>
       <c r="CV19" s="36">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>164.005</v>
       </c>
       <c r="CW19" s="36">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>164.77431999999999</v>
       </c>
       <c r="CX19" s="36">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>496.76127599999995</v>
       </c>
       <c r="CY19" s="36">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>510.56018640000002</v>
       </c>
       <c r="CZ19" s="36">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>564.35818904000007</v>
       </c>
       <c r="DA19" s="36">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>551.96917451999991</v>
       </c>
       <c r="DB19" s="36">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>558.27466726</v>
       </c>
       <c r="DC19" s="20">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>357.94338163000009</v>
       </c>
       <c r="DD19" s="20">
@@ -7431,43 +7432,43 @@
         <v>1691.4650000000006</v>
       </c>
       <c r="DL19" s="20">
-        <f t="shared" ref="DL19:DU19" si="64">(DL14-DL18)</f>
+        <f t="shared" ref="DL19:DU19" si="66">(DL14-DL18)</f>
         <v>2290.1655000000005</v>
       </c>
       <c r="DM19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>2394.1244250000004</v>
       </c>
       <c r="DN19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>2552.31498375</v>
       </c>
       <c r="DO19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>2772.3378965625006</v>
       </c>
       <c r="DP19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>3063.6336695343753</v>
       </c>
       <c r="DQ19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>3437.8188334776569</v>
       </c>
       <c r="DR19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>2021.5057905457734</v>
       </c>
       <c r="DS19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>1285.8300726446851</v>
       </c>
       <c r="DT19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>893.08791485523068</v>
       </c>
       <c r="DU19" s="20">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>674.17279606057105</v>
       </c>
     </row>
@@ -7713,31 +7714,31 @@
         <v>0</v>
       </c>
       <c r="CX20" s="35">
-        <f t="shared" ref="CX20:DD20" si="65">CW39*$DY$28</f>
+        <f t="shared" ref="CX20:DD20" si="67">CW39*$DY$28</f>
         <v>27.544615400000005</v>
       </c>
       <c r="CY20" s="35">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>44.584556870500002</v>
       </c>
       <c r="CZ20" s="35">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>62.62676102679125</v>
       </c>
       <c r="DA20" s="35">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>83.003771903961962</v>
       </c>
       <c r="DB20" s="35">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>103.64039266274072</v>
       </c>
       <c r="DC20" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>125.1526321102298</v>
       </c>
       <c r="DD20" s="16">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>140.85325255678728</v>
       </c>
       <c r="DE20" s="16"/>
@@ -7746,11 +7747,11 @@
       <c r="DH20" s="16"/>
       <c r="DI20" s="12"/>
       <c r="DJ20" s="16">
-        <f t="shared" ref="DJ20" si="66">SUM(CA20:CD20)</f>
+        <f t="shared" ref="DJ20" si="68">SUM(CA20:CD20)</f>
         <v>164.6</v>
       </c>
       <c r="DK20" s="16">
-        <f t="shared" ref="DK20" si="67">SUM(CE20:CH20)</f>
+        <f t="shared" ref="DK20" si="69">SUM(CE20:CH20)</f>
         <v>175.8</v>
       </c>
       <c r="DL20" s="16">
@@ -7758,39 +7759,39 @@
         <v>175.8</v>
       </c>
       <c r="DM20" s="16">
-        <f t="shared" ref="DM20:DU20" si="68">+DL20</f>
+        <f t="shared" ref="DM20:DU20" si="70">+DL20</f>
         <v>175.8</v>
       </c>
       <c r="DN20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
       <c r="DO20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
       <c r="DP20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
       <c r="DQ20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
       <c r="DR20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
       <c r="DS20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
       <c r="DT20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
       <c r="DU20" s="16">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>175.8</v>
       </c>
     </row>
@@ -7811,23 +7812,23 @@
         <v>15.763</v>
       </c>
       <c r="F21" s="16">
-        <f t="shared" ref="F21:L21" si="69">F19+F20</f>
+        <f t="shared" ref="F21:L21" si="71">F19+F20</f>
         <v>11.916</v>
       </c>
       <c r="G21" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>4.1849999999999952</v>
       </c>
       <c r="H21" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>12.383000000000006</v>
       </c>
       <c r="I21" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>14.100000000000007</v>
       </c>
       <c r="J21" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>7.7899999999999991</v>
       </c>
       <c r="K21" s="16">
@@ -7835,79 +7836,79 @@
         <v>6.7870000000000026</v>
       </c>
       <c r="L21" s="16">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>8.9120000000000026</v>
       </c>
       <c r="M21" s="16">
-        <f t="shared" ref="M21:U21" si="70">M19+M20</f>
+        <f t="shared" ref="M21:U21" si="72">M19+M20</f>
         <v>17.015000000000004</v>
       </c>
       <c r="N21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>-5.118000000000003</v>
       </c>
       <c r="O21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>17.956999999999997</v>
       </c>
       <c r="P21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>30.214000000000002</v>
       </c>
       <c r="Q21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>19.878999999999994</v>
       </c>
       <c r="R21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>20.298000000000016</v>
       </c>
       <c r="S21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>19.995999999999999</v>
       </c>
       <c r="T21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>34.402999999999984</v>
       </c>
       <c r="U21" s="16">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>9.4910000000000085</v>
       </c>
       <c r="V21" s="16">
-        <f t="shared" ref="V21:AD21" si="71">V19+V20</f>
+        <f t="shared" ref="V21:AD21" si="73">V19+V20</f>
         <v>-4.8259999999999827</v>
       </c>
       <c r="W21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>28.681000000000022</v>
       </c>
       <c r="X21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>56.91900000000004</v>
       </c>
       <c r="Y21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>57.733999999999973</v>
       </c>
       <c r="Z21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>4.5050000000000168</v>
       </c>
       <c r="AA21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>36.960000000000008</v>
       </c>
       <c r="AB21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>67.360880000000009</v>
       </c>
       <c r="AC21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>34.786720000000003</v>
       </c>
       <c r="AD21" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>25.666719999999998</v>
       </c>
       <c r="AE21" s="16"/>
@@ -7944,11 +7945,11 @@
       <c r="BJ21" s="35"/>
       <c r="BK21" s="35"/>
       <c r="BL21" s="35">
-        <f t="shared" ref="BL21:BM21" si="72">BL19+BL20</f>
+        <f t="shared" ref="BL21:BM21" si="74">BL19+BL20</f>
         <v>142.1</v>
       </c>
       <c r="BM21" s="35">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>222.60000000000002</v>
       </c>
       <c r="BN21" s="35">
@@ -7960,7 +7961,7 @@
         <v>159.20000000000002</v>
       </c>
       <c r="BP21" s="35">
-        <f t="shared" ref="BP21" si="73">BP19+BP20</f>
+        <f t="shared" ref="BP21" si="75">BP19+BP20</f>
         <v>221.50000000000009</v>
       </c>
       <c r="BQ21" s="35">
@@ -7984,55 +7985,55 @@
         <v>312.5</v>
       </c>
       <c r="BV21" s="35">
-        <f t="shared" ref="BV21:CH21" si="74">BV19+BV20</f>
+        <f t="shared" ref="BV21:CH21" si="76">BV19+BV20</f>
         <v>232.9</v>
       </c>
       <c r="BW21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>299.40000000000003</v>
       </c>
       <c r="BX21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>335.19999999999987</v>
       </c>
       <c r="BY21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>351.79999999999995</v>
       </c>
       <c r="BZ21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>295.39999999999992</v>
       </c>
       <c r="CA21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>398.60000000000008</v>
       </c>
       <c r="CB21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>355.30000000000013</v>
       </c>
       <c r="CC21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>388.60000000000008</v>
       </c>
       <c r="CD21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>432.1</v>
       </c>
       <c r="CE21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>459.60000000000008</v>
       </c>
       <c r="CF21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>467.99999999999989</v>
       </c>
       <c r="CG21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>471.80000000000007</v>
       </c>
       <c r="CH21" s="35">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>467.86500000000001</v>
       </c>
       <c r="CI21" s="35"/>
@@ -8043,15 +8044,15 @@
       <c r="CN21" s="35"/>
       <c r="CO21" s="48"/>
       <c r="CP21" s="35">
-        <f t="shared" ref="CP21:DC21" si="75">SUM(CP19:CP20)</f>
+        <f t="shared" ref="CP21:DC21" si="77">SUM(CP19:CP20)</f>
         <v>15.449999999999994</v>
       </c>
       <c r="CQ21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>47.521999999999991</v>
       </c>
       <c r="CR21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>39.908000000000015</v>
       </c>
       <c r="CS21" s="35">
@@ -8063,39 +8064,39 @@
         <v>78.590000000000032</v>
       </c>
       <c r="CU21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>62.70900000000006</v>
       </c>
       <c r="CV21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>147.839</v>
       </c>
       <c r="CW21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>164.77431999999999</v>
       </c>
       <c r="CX21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>524.30589139999995</v>
       </c>
       <c r="CY21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>555.14474327050004</v>
       </c>
       <c r="CZ21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>626.98495006679127</v>
       </c>
       <c r="DA21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>634.97294642396184</v>
       </c>
       <c r="DB21" s="35">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>661.91505992274074</v>
       </c>
       <c r="DC21" s="16">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>483.09601374022986</v>
       </c>
       <c r="DD21" s="16">
@@ -8108,51 +8109,51 @@
       <c r="DH21" s="16"/>
       <c r="DI21" s="12"/>
       <c r="DJ21" s="16">
-        <f t="shared" ref="DJ21:DK21" si="76">SUM(DJ19:DJ20)</f>
+        <f t="shared" ref="DJ21:DK21" si="78">SUM(DJ19:DJ20)</f>
         <v>1574.6000000000001</v>
       </c>
       <c r="DK21" s="16">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>1867.2650000000006</v>
       </c>
       <c r="DL21" s="16">
-        <f t="shared" ref="DL21" si="77">SUM(DL19:DL20)</f>
+        <f t="shared" ref="DL21" si="79">SUM(DL19:DL20)</f>
         <v>2465.9655000000007</v>
       </c>
       <c r="DM21" s="16">
-        <f t="shared" ref="DM21" si="78">SUM(DM19:DM20)</f>
+        <f t="shared" ref="DM21" si="80">SUM(DM19:DM20)</f>
         <v>2569.9244250000006</v>
       </c>
       <c r="DN21" s="16">
-        <f t="shared" ref="DN21" si="79">SUM(DN19:DN20)</f>
+        <f t="shared" ref="DN21" si="81">SUM(DN19:DN20)</f>
         <v>2728.1149837500002</v>
       </c>
       <c r="DO21" s="16">
-        <f t="shared" ref="DO21" si="80">SUM(DO19:DO20)</f>
+        <f t="shared" ref="DO21" si="82">SUM(DO19:DO20)</f>
         <v>2948.1378965625008</v>
       </c>
       <c r="DP21" s="16">
-        <f t="shared" ref="DP21" si="81">SUM(DP19:DP20)</f>
+        <f t="shared" ref="DP21" si="83">SUM(DP19:DP20)</f>
         <v>3239.4336695343754</v>
       </c>
       <c r="DQ21" s="16">
-        <f t="shared" ref="DQ21" si="82">SUM(DQ19:DQ20)</f>
+        <f t="shared" ref="DQ21" si="84">SUM(DQ19:DQ20)</f>
         <v>3613.6188334776571</v>
       </c>
       <c r="DR21" s="16">
-        <f t="shared" ref="DR21" si="83">SUM(DR19:DR20)</f>
+        <f t="shared" ref="DR21" si="85">SUM(DR19:DR20)</f>
         <v>2197.3057905457736</v>
       </c>
       <c r="DS21" s="16">
-        <f t="shared" ref="DS21" si="84">SUM(DS19:DS20)</f>
+        <f t="shared" ref="DS21" si="86">SUM(DS19:DS20)</f>
         <v>1461.630072644685</v>
       </c>
       <c r="DT21" s="16">
-        <f t="shared" ref="DT21" si="85">SUM(DT19:DT20)</f>
+        <f t="shared" ref="DT21" si="87">SUM(DT19:DT20)</f>
         <v>1068.8879148552307</v>
       </c>
       <c r="DU21" s="16">
-        <f t="shared" ref="DU21" si="86">SUM(DU19:DU20)</f>
+        <f t="shared" ref="DU21" si="88">SUM(DU19:DU20)</f>
         <v>849.972796060571</v>
       </c>
     </row>
@@ -8370,7 +8371,7 @@
         <v>29.151300000000006</v>
       </c>
       <c r="CU22" s="35">
-        <f t="shared" ref="CU22:DC22" si="87">CU21*CU37</f>
+        <f t="shared" ref="CU22:DC22" si="89">CU21*CU37</f>
         <v>21.94815000000002</v>
       </c>
       <c r="CV22" s="35">
@@ -8381,27 +8382,27 @@
         <v>57.671012000000005</v>
       </c>
       <c r="CX22" s="35">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>183.50706198999998</v>
       </c>
       <c r="CY22" s="35">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>194.30066014467499</v>
       </c>
       <c r="CZ22" s="35">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>219.44473252337693</v>
       </c>
       <c r="DA22" s="35">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>222.24053124838665</v>
       </c>
       <c r="DB22" s="35">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>231.67027097295923</v>
       </c>
       <c r="DC22" s="16">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>169.08360480908044</v>
       </c>
       <c r="DD22" s="16">
@@ -8414,11 +8415,11 @@
       <c r="DH22" s="16"/>
       <c r="DI22" s="12"/>
       <c r="DJ22" s="16">
-        <f t="shared" ref="DJ22" si="88">SUM(CA22:CD22)</f>
+        <f t="shared" ref="DJ22" si="90">SUM(CA22:CD22)</f>
         <v>343.9</v>
       </c>
       <c r="DK22" s="16">
-        <f t="shared" ref="DK22" si="89">SUM(CE22:CH22)</f>
+        <f t="shared" ref="DK22" si="91">SUM(CE22:CH22)</f>
         <v>393.07299999999998</v>
       </c>
       <c r="DL22" s="16">
@@ -8426,39 +8427,39 @@
         <v>493.19310000000019</v>
       </c>
       <c r="DM22" s="16">
-        <f t="shared" ref="DM22:DU22" si="90">+DM21*0.2</f>
+        <f t="shared" ref="DM22:DU22" si="92">+DM21*0.2</f>
         <v>513.98488500000019</v>
       </c>
       <c r="DN22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>545.62299675000008</v>
       </c>
       <c r="DO22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>589.62757931250019</v>
       </c>
       <c r="DP22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>647.88673390687518</v>
       </c>
       <c r="DQ22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>722.72376669553148</v>
       </c>
       <c r="DR22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>439.46115810915472</v>
       </c>
       <c r="DS22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>292.32601452893704</v>
       </c>
       <c r="DT22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>213.77758297104617</v>
       </c>
       <c r="DU22" s="16">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>169.99455921211421</v>
       </c>
     </row>
@@ -8467,35 +8468,35 @@
         <v>12</v>
       </c>
       <c r="C23" s="16">
-        <f t="shared" ref="C23:J23" si="91">C21-C22</f>
+        <f t="shared" ref="C23:J23" si="93">C21-C22</f>
         <v>7.6609999999999969</v>
       </c>
       <c r="D23" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>12.181000000000001</v>
       </c>
       <c r="E23" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>15.763</v>
       </c>
       <c r="F23" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>29.41</v>
       </c>
       <c r="G23" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>2.3069999999999951</v>
       </c>
       <c r="H23" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>6.2220000000000066</v>
       </c>
       <c r="I23" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>8.4780000000000069</v>
       </c>
       <c r="J23" s="16">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>55.508000000000003</v>
       </c>
       <c r="K23" s="16">
@@ -8503,79 +8504,79 @@
         <v>8.2320000000000029</v>
       </c>
       <c r="L23" s="16">
-        <f t="shared" ref="L23:U23" si="92">L21-L22</f>
+        <f t="shared" ref="L23:U23" si="94">L21-L22</f>
         <v>5.8060000000000027</v>
       </c>
       <c r="M23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>14.848000000000004</v>
       </c>
       <c r="N23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>1.9859999999999971</v>
       </c>
       <c r="O23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>11.402999999999997</v>
       </c>
       <c r="P23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>21.977000000000004</v>
       </c>
       <c r="Q23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>12.622999999999994</v>
       </c>
       <c r="R23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>13.19370000000001</v>
       </c>
       <c r="S23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>13.196999999999999</v>
       </c>
       <c r="T23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>32.466999999999985</v>
       </c>
       <c r="U23" s="16">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>12.382000000000009</v>
       </c>
       <c r="V23" s="16">
-        <f t="shared" ref="V23:AD23" si="93">V21-V22</f>
+        <f t="shared" ref="V23:AD23" si="95">V21-V22</f>
         <v>-6.2289999999999832</v>
       </c>
       <c r="W23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>18.929000000000023</v>
       </c>
       <c r="X23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>37.707000000000036</v>
       </c>
       <c r="Y23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>39.735999999999976</v>
       </c>
       <c r="Z23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>9.5440000000000165</v>
       </c>
       <c r="AA23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>24.024000000000008</v>
       </c>
       <c r="AB23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>43.784572000000011</v>
       </c>
       <c r="AC23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>22.611368000000002</v>
       </c>
       <c r="AD23" s="16">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>16.683368000000002</v>
       </c>
       <c r="AE23" s="16"/>
@@ -8612,11 +8613,11 @@
       <c r="BJ23" s="35"/>
       <c r="BK23" s="35"/>
       <c r="BL23" s="35">
-        <f t="shared" ref="BL23" si="94">BL21-BL22</f>
+        <f t="shared" ref="BL23" si="96">BL21-BL22</f>
         <v>115.3</v>
       </c>
       <c r="BM23" s="35">
-        <f t="shared" ref="BM23" si="95">BM21-BM22</f>
+        <f t="shared" ref="BM23" si="97">BM21-BM22</f>
         <v>174.8</v>
       </c>
       <c r="BN23" s="35">
@@ -8628,11 +8629,11 @@
         <v>155.00000000000003</v>
       </c>
       <c r="BP23" s="35">
-        <f t="shared" ref="BP23:BQ23" si="96">BP21-BP22</f>
+        <f t="shared" ref="BP23:BQ23" si="98">BP21-BP22</f>
         <v>177.60000000000008</v>
       </c>
       <c r="BQ23" s="35">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>186.20000000000005</v>
       </c>
       <c r="BR23" s="35">
@@ -8652,55 +8653,55 @@
         <v>239.3</v>
       </c>
       <c r="BV23" s="35">
-        <f t="shared" ref="BV23:CH23" si="97">BV21-BV22</f>
+        <f t="shared" ref="BV23:CH23" si="99">BV21-BV22</f>
         <v>186.2</v>
       </c>
       <c r="BW23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>248.40000000000003</v>
       </c>
       <c r="BX23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>259.19999999999987</v>
       </c>
       <c r="BY23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>267.59999999999997</v>
       </c>
       <c r="BZ23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>217.09999999999991</v>
       </c>
       <c r="CA23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>306.60000000000008</v>
       </c>
       <c r="CB23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>278.10000000000014</v>
       </c>
       <c r="CC23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>309.10000000000008</v>
       </c>
       <c r="CD23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>336.90000000000003</v>
       </c>
       <c r="CE23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>358.30000000000007</v>
       </c>
       <c r="CF23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>369.09999999999991</v>
       </c>
       <c r="CG23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>372.50000000000006</v>
       </c>
       <c r="CH23" s="35">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>374.29200000000003</v>
       </c>
       <c r="CI23" s="35"/>
@@ -8711,15 +8712,15 @@
       <c r="CN23" s="35"/>
       <c r="CO23" s="48"/>
       <c r="CP23" s="35">
-        <f t="shared" ref="CP23:DB23" si="98">CP21-CP22</f>
+        <f t="shared" ref="CP23:DB23" si="100">CP21-CP22</f>
         <v>15.449999999999994</v>
       </c>
       <c r="CQ23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>65.015999999999991</v>
       </c>
       <c r="CR23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>73.965000000000018</v>
       </c>
       <c r="CS23" s="35">
@@ -8731,35 +8732,35 @@
         <v>49.438700000000026</v>
       </c>
       <c r="CU23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>40.76085000000004</v>
       </c>
       <c r="CV23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>105.916</v>
       </c>
       <c r="CW23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>107.10330799999998</v>
       </c>
       <c r="CX23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>340.79882940999994</v>
       </c>
       <c r="CY23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>360.84408312582502</v>
       </c>
       <c r="CZ23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>407.54021754341431</v>
       </c>
       <c r="DA23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>412.73241517557517</v>
       </c>
       <c r="DB23" s="35">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>430.24478894978154</v>
       </c>
       <c r="DC23" s="16">
@@ -8771,295 +8772,295 @@
         <v>253.00325815166175</v>
       </c>
       <c r="DE23" s="16">
-        <f t="shared" ref="DE23:DK23" si="99">+DE21-DE22</f>
+        <f t="shared" ref="DE23:DK23" si="101">+DE21-DE22</f>
         <v>0</v>
       </c>
       <c r="DF23" s="16">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="DG23" s="16">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="DH23" s="16">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="DI23" s="16">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="DJ23" s="16">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>1230.7000000000003</v>
       </c>
       <c r="DK23" s="16">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>1474.1920000000005</v>
       </c>
       <c r="DL23" s="16">
-        <f t="shared" ref="DL23" si="100">+DL21-DL22</f>
+        <f t="shared" ref="DL23" si="102">+DL21-DL22</f>
         <v>1972.7724000000005</v>
       </c>
       <c r="DM23" s="16">
-        <f t="shared" ref="DM23" si="101">+DM21-DM22</f>
+        <f t="shared" ref="DM23" si="103">+DM21-DM22</f>
         <v>2055.9395400000003</v>
       </c>
       <c r="DN23" s="16">
-        <f t="shared" ref="DN23" si="102">+DN21-DN22</f>
+        <f t="shared" ref="DN23" si="104">+DN21-DN22</f>
         <v>2182.4919870000003</v>
       </c>
       <c r="DO23" s="16">
-        <f t="shared" ref="DO23" si="103">+DO21-DO22</f>
+        <f t="shared" ref="DO23" si="105">+DO21-DO22</f>
         <v>2358.5103172500008</v>
       </c>
       <c r="DP23" s="16">
-        <f t="shared" ref="DP23" si="104">+DP21-DP22</f>
+        <f t="shared" ref="DP23" si="106">+DP21-DP22</f>
         <v>2591.5469356275003</v>
       </c>
       <c r="DQ23" s="16">
-        <f t="shared" ref="DQ23" si="105">+DQ21-DQ22</f>
+        <f t="shared" ref="DQ23" si="107">+DQ21-DQ22</f>
         <v>2890.8950667821255</v>
       </c>
       <c r="DR23" s="16">
-        <f t="shared" ref="DR23" si="106">+DR21-DR22</f>
+        <f t="shared" ref="DR23" si="108">+DR21-DR22</f>
         <v>1757.8446324366189</v>
       </c>
       <c r="DS23" s="16">
-        <f t="shared" ref="DS23" si="107">+DS21-DS22</f>
+        <f t="shared" ref="DS23" si="109">+DS21-DS22</f>
         <v>1169.3040581157479</v>
       </c>
       <c r="DT23" s="16">
-        <f t="shared" ref="DT23" si="108">+DT21-DT22</f>
+        <f t="shared" ref="DT23" si="110">+DT21-DT22</f>
         <v>855.11033188418457</v>
       </c>
       <c r="DU23" s="16">
-        <f t="shared" ref="DU23" si="109">+DU21-DU22</f>
+        <f t="shared" ref="DU23" si="111">+DU21-DU22</f>
         <v>679.97823684845685</v>
       </c>
       <c r="DV23" s="12">
-        <f t="shared" ref="DD23:EI23" si="110">DU23*(1+$DY$29)</f>
+        <f t="shared" ref="DV23:EI23" si="112">DU23*(1+$DY$29)</f>
         <v>543.98258947876548</v>
       </c>
       <c r="DW23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>435.18607158301239</v>
       </c>
       <c r="DX23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>348.14885726640995</v>
       </c>
       <c r="DY23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>278.51908581312796</v>
       </c>
       <c r="DZ23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>222.81526865050239</v>
       </c>
       <c r="EA23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>178.25221492040191</v>
       </c>
       <c r="EB23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>142.60177193632154</v>
       </c>
       <c r="EC23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>114.08141754905724</v>
       </c>
       <c r="ED23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>91.265134039245794</v>
       </c>
       <c r="EE23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>73.012107231396641</v>
       </c>
       <c r="EF23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>58.409685785117318</v>
       </c>
       <c r="EG23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>46.727748628093856</v>
       </c>
       <c r="EH23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>37.382198902475089</v>
       </c>
       <c r="EI23" s="12">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>29.905759121980072</v>
       </c>
       <c r="EJ23" s="12">
-        <f t="shared" ref="EJ23:FO23" si="111">EI23*(1+$DY$29)</f>
+        <f t="shared" ref="EJ23:FO23" si="113">EI23*(1+$DY$29)</f>
         <v>23.92460729758406</v>
       </c>
       <c r="EK23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>19.139685838067248</v>
       </c>
       <c r="EL23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>15.311748670453799</v>
       </c>
       <c r="EM23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>12.24939893636304</v>
       </c>
       <c r="EN23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>9.7995191490904325</v>
       </c>
       <c r="EO23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>7.8396153192723466</v>
       </c>
       <c r="EP23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>6.2716922554178778</v>
       </c>
       <c r="EQ23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>5.0173538043343022</v>
       </c>
       <c r="ER23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>4.013883043467442</v>
       </c>
       <c r="ES23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>3.2111064347739537</v>
       </c>
       <c r="ET23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.568885147819163</v>
       </c>
       <c r="EU23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.0551081182553306</v>
       </c>
       <c r="EV23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.6440864946042646</v>
       </c>
       <c r="EW23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.3152691956834117</v>
       </c>
       <c r="EX23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>1.0522153565467294</v>
       </c>
       <c r="EY23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.84177228523738357</v>
       </c>
       <c r="EZ23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.67341782818990692</v>
       </c>
       <c r="FA23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.53873426255192558</v>
       </c>
       <c r="FB23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.43098741004154051</v>
       </c>
       <c r="FC23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.34478992803323244</v>
       </c>
       <c r="FD23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.27583194242658599</v>
       </c>
       <c r="FE23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.2206655539412688</v>
       </c>
       <c r="FF23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.17653244315301506</v>
       </c>
       <c r="FG23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.14122595452241204</v>
       </c>
       <c r="FH23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>0.11298076361792964</v>
       </c>
       <c r="FI23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>9.0384610894343714E-2</v>
       </c>
       <c r="FJ23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>7.230768871547498E-2</v>
       </c>
       <c r="FK23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>5.7846150972379988E-2</v>
       </c>
       <c r="FL23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>4.627692077790399E-2</v>
       </c>
       <c r="FM23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>3.7021536622323194E-2</v>
       </c>
       <c r="FN23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.9617229297858556E-2</v>
       </c>
       <c r="FO23" s="12">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>2.3693783438286847E-2</v>
       </c>
       <c r="FP23" s="12">
-        <f t="shared" ref="FP23:FY23" si="112">FO23*(1+$DY$29)</f>
+        <f t="shared" ref="FP23:FY23" si="114">FO23*(1+$DY$29)</f>
         <v>1.8955026750629479E-2</v>
       </c>
       <c r="FQ23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1.5164021400503583E-2</v>
       </c>
       <c r="FR23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>1.2131217120402868E-2</v>
       </c>
       <c r="FS23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>9.7049736963222954E-3</v>
       </c>
       <c r="FT23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>7.763978957057837E-3</v>
       </c>
       <c r="FU23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>6.2111831656462696E-3</v>
       </c>
       <c r="FV23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>4.9689465325170159E-3</v>
       </c>
       <c r="FW23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>3.9751572260136132E-3</v>
       </c>
       <c r="FX23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>3.1801257808108906E-3</v>
       </c>
       <c r="FY23" s="12">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>2.5441006246487126E-3</v>
       </c>
     </row>
@@ -9080,47 +9081,47 @@
         <v>0.61315543799595462</v>
       </c>
       <c r="F24" s="21">
-        <f t="shared" ref="F24:L24" si="113">F23/F25</f>
+        <f t="shared" ref="F24:L24" si="115">F23/F25</f>
         <v>1.1383781691503774</v>
       </c>
       <c r="G24" s="21">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>9.0085516810496105E-2</v>
       </c>
       <c r="H24" s="21">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.2455018939393942</v>
       </c>
       <c r="I24" s="21">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.34024962876750836</v>
       </c>
       <c r="J24" s="21">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>2.4245653883113483</v>
       </c>
       <c r="K24" s="21">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.38642444726094927</v>
       </c>
       <c r="L24" s="21">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>0.26366939146230711</v>
       </c>
       <c r="M24" s="21">
-        <f t="shared" ref="M24:U24" si="114">M23/M25</f>
+        <f t="shared" ref="M24:U24" si="116">M23/M25</f>
         <v>0.66158713184511886</v>
       </c>
       <c r="N24" s="21">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>8.3635138549650351E-2</v>
       </c>
       <c r="O24" s="21">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0.47362518690812411</v>
       </c>
       <c r="P24" s="21">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0.90336238079579101</v>
       </c>
       <c r="Q24" s="21">
@@ -9128,55 +9129,55 @@
         <v>0.49536928027627325</v>
       </c>
       <c r="R24" s="21">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0.55606271336452184</v>
       </c>
       <c r="S24" s="21">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0.48604154390100174</v>
       </c>
       <c r="T24" s="21">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>1.2255860480918042</v>
       </c>
       <c r="U24" s="21">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>0.21476766170017186</v>
       </c>
       <c r="V24" s="21">
-        <f t="shared" ref="V24:AD24" si="115">V23/V25</f>
+        <f t="shared" ref="V24:AD24" si="117">V23/V25</f>
         <v>-0.11551014353002231</v>
       </c>
       <c r="W24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.34561522028884994</v>
       </c>
       <c r="X24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.67277463557371564</v>
       </c>
       <c r="Y24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.7028442054620061</v>
       </c>
       <c r="Z24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.16881279184944134</v>
       </c>
       <c r="AA24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.42493278618933084</v>
       </c>
       <c r="AB24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.77445471911702302</v>
       </c>
       <c r="AC24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.39994637045422388</v>
       </c>
       <c r="AD24" s="21">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>0.29509282581010332</v>
       </c>
       <c r="AE24" s="21"/>
@@ -9213,11 +9214,11 @@
       <c r="BJ24" s="37"/>
       <c r="BK24" s="37"/>
       <c r="BL24" s="37">
-        <f t="shared" ref="BL24:BM24" si="116">BL23/BL25</f>
+        <f t="shared" ref="BL24:BM24" si="118">BL23/BL25</f>
         <v>2.5968468468468471</v>
       </c>
       <c r="BM24" s="37">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>3.9192825112107625</v>
       </c>
       <c r="BN24" s="37">
@@ -9229,11 +9230,11 @@
         <v>3.3405172413793109</v>
       </c>
       <c r="BP24" s="37">
-        <f t="shared" ref="BP24" si="117">BP23/BP25</f>
+        <f t="shared" ref="BP24" si="119">BP23/BP25</f>
         <v>3.7547568710359429</v>
       </c>
       <c r="BQ24" s="37">
-        <f t="shared" ref="BQ24" si="118">BQ23/BQ25</f>
+        <f t="shared" ref="BQ24" si="120">BQ23/BQ25</f>
         <v>3.9117647058823537</v>
       </c>
       <c r="BR24" s="37">
@@ -9253,55 +9254,55 @@
         <v>4.9137577002053385</v>
       </c>
       <c r="BV24" s="37">
-        <f t="shared" ref="BV24:CD24" si="119">BV23/BV25</f>
+        <f t="shared" ref="BV24:CD24" si="121">BV23/BV25</f>
         <v>3.7692307692307692</v>
       </c>
       <c r="BW24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>5.0080645161290329</v>
       </c>
       <c r="BX24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>5.2363636363636337</v>
       </c>
       <c r="BY24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>5.3843058350100597</v>
       </c>
       <c r="BZ24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>4.3594377510040143</v>
       </c>
       <c r="CA24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>6.1690140845070438</v>
       </c>
       <c r="CB24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>5.8547368421052663</v>
       </c>
       <c r="CC24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>6.3863636363636385</v>
       </c>
       <c r="CD24" s="37">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>6.9178644763860371</v>
       </c>
       <c r="CE24" s="37">
-        <f t="shared" ref="CE24:CH24" si="120">CE23/CE25</f>
+        <f t="shared" ref="CE24:CH24" si="122">CE23/CE25</f>
         <v>7.3724279835390956</v>
       </c>
       <c r="CF24" s="37">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>7.6418219461697712</v>
       </c>
       <c r="CG24" s="37">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>7.8752642706131093</v>
       </c>
       <c r="CH24" s="37">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>7.9131501057082465</v>
       </c>
       <c r="CI24" s="37"/>
@@ -9312,15 +9313,15 @@
       <c r="CN24" s="37"/>
       <c r="CO24" s="50"/>
       <c r="CP24" s="37">
-        <f t="shared" ref="CP24:DD24" si="121">CP23/CP25</f>
+        <f t="shared" ref="CP24:DD24" si="123">CP23/CP25</f>
         <v>0.66164189970450926</v>
       </c>
       <c r="CQ24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>2.5793858605094022</v>
       </c>
       <c r="CR24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>3.0642555306984844</v>
       </c>
       <c r="CS24" s="37">
@@ -9332,7 +9333,7 @@
         <v>2.0259063854199759</v>
       </c>
       <c r="CU24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0.98681410465918695</v>
       </c>
       <c r="CV24" s="37">
@@ -9340,35 +9341,35 @@
         <v>1.8865733319083751</v>
       </c>
       <c r="CW24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>1.8944267015706804</v>
       </c>
       <c r="CX24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>6.0279968411277753</v>
       </c>
       <c r="CY24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>6.3825541800945418</v>
       </c>
       <c r="CZ24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7.2085081637083332</v>
       </c>
       <c r="DA24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7.3003469501835143</v>
       </c>
       <c r="DB24" s="37">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>7.6101031015597416</v>
       </c>
       <c r="DC24" s="21">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>5.5542027899241084</v>
       </c>
       <c r="DD24" s="21">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>4.4750823926641745</v>
       </c>
       <c r="DE24" s="22"/>
@@ -9617,31 +9618,31 @@
         <v>56.536000000000001</v>
       </c>
       <c r="CX25" s="35">
-        <f t="shared" ref="CX25:DD25" si="122">CW25</f>
+        <f t="shared" ref="CX25:DD25" si="124">CW25</f>
         <v>56.536000000000001</v>
       </c>
       <c r="CY25" s="35">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>56.536000000000001</v>
       </c>
       <c r="CZ25" s="35">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>56.536000000000001</v>
       </c>
       <c r="DA25" s="35">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>56.536000000000001</v>
       </c>
       <c r="DB25" s="35">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>56.536000000000001</v>
       </c>
       <c r="DC25" s="16">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>56.536000000000001</v>
       </c>
       <c r="DD25" s="16">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>56.536000000000001</v>
       </c>
       <c r="DE25" s="24"/>
@@ -9921,71 +9922,71 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="23">
-        <f t="shared" ref="G28:W28" si="123">+G12/C12-1</f>
+        <f t="shared" ref="G28:W28" si="125">+G12/C12-1</f>
         <v>0.4290515792648768</v>
       </c>
       <c r="H28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.33895598363110091</v>
       </c>
       <c r="I28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.22378067252347789</v>
       </c>
       <c r="J28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.54603420937215352</v>
       </c>
       <c r="K28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.21122301290556056</v>
       </c>
       <c r="L28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.28788669399925459</v>
       </c>
       <c r="M28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.46161843701264926</v>
       </c>
       <c r="N28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.3070745864792912</v>
       </c>
       <c r="O28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.54464885857253087</v>
       </c>
       <c r="P28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.32268333622735423</v>
       </c>
       <c r="Q28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.27075959014311102</v>
       </c>
       <c r="R28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.26651975024207841</v>
       </c>
       <c r="S28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.28499363385820442</v>
       </c>
       <c r="T28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.22498395472314603</v>
       </c>
       <c r="U28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.29564719053203969</v>
       </c>
       <c r="V28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.4358044870949882</v>
       </c>
       <c r="W28" s="23">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>0.61645553743885628</v>
       </c>
       <c r="X28" s="23">
@@ -10042,7 +10043,7 @@
       <c r="BN28" s="39"/>
       <c r="BO28" s="39"/>
       <c r="BP28" s="39">
-        <f t="shared" ref="BP28" si="124">BP12/BL12-1</f>
+        <f t="shared" ref="BP28" si="126">BP12/BL12-1</f>
         <v>0.23342541436464104</v>
       </c>
       <c r="BQ28" s="39">
@@ -10058,79 +10059,79 @@
         <v>0.21841202848852537</v>
       </c>
       <c r="BT28" s="39">
-        <f t="shared" ref="BT28:BU28" si="125">BT12/BP12-1</f>
+        <f t="shared" ref="BT28:BU28" si="127">BT12/BP12-1</f>
         <v>4.5688689809630256E-2</v>
       </c>
       <c r="BU28" s="39">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>0.16033280863503463</v>
       </c>
       <c r="BV28" s="39">
-        <f t="shared" ref="BV28" si="126">BV12/BR12-1</f>
+        <f t="shared" ref="BV28" si="128">BV12/BR12-1</f>
         <v>0.18376685934489401</v>
       </c>
       <c r="BW28" s="39">
-        <f t="shared" ref="BW28" si="127">BW12/BS12-1</f>
+        <f t="shared" ref="BW28" si="129">BW12/BS12-1</f>
         <v>9.7423684780255426E-2</v>
       </c>
       <c r="BX28" s="39">
-        <f t="shared" ref="BX28" si="128">BX12/BT12-1</f>
+        <f t="shared" ref="BX28" si="130">BX12/BT12-1</f>
         <v>0.2775754979653029</v>
       </c>
       <c r="BY28" s="39">
-        <f t="shared" ref="BY28" si="129">BY12/BU12-1</f>
+        <f t="shared" ref="BY28" si="131">BY12/BU12-1</f>
         <v>0.18100775193798446</v>
       </c>
       <c r="BZ28" s="39">
-        <f t="shared" ref="BZ28:CD28" si="130">BZ12/BV12-1</f>
+        <f t="shared" ref="BZ28:CD28" si="132">BZ12/BV12-1</f>
         <v>0.25066124109867749</v>
       </c>
       <c r="CA28" s="39">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.3369500887749064</v>
       </c>
       <c r="CB28" s="39">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.19849119865884357</v>
       </c>
       <c r="CC28" s="39">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.22891368559238612</v>
       </c>
       <c r="CD28" s="39">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>0.19716935090287957</v>
       </c>
       <c r="CE28" s="39">
-        <f t="shared" ref="CE28:CG28" si="131">CE12/CA12-1</f>
+        <f t="shared" ref="CE28:CG28" si="133">CE12/CA12-1</f>
         <v>0.17220008853474988</v>
       </c>
       <c r="CF28" s="39">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>0.11707931179185871</v>
       </c>
       <c r="CG28" s="39">
-        <f t="shared" si="131"/>
+        <f t="shared" si="133"/>
         <v>6.7565763119241673E-2</v>
       </c>
       <c r="CH28" s="39">
-        <f t="shared" ref="CH28" si="132">CH12/CD12-1</f>
+        <f t="shared" ref="CH28" si="134">CH12/CD12-1</f>
         <v>8.6424785976355611E-2</v>
       </c>
       <c r="CI28" s="39">
-        <f t="shared" ref="CI28" si="133">CI12/CE12-1</f>
+        <f t="shared" ref="CI28" si="135">CI12/CE12-1</f>
         <v>-1</v>
       </c>
       <c r="CJ28" s="39">
-        <f t="shared" ref="CJ28" si="134">CJ12/CF12-1</f>
+        <f t="shared" ref="CJ28" si="136">CJ12/CF12-1</f>
         <v>-1</v>
       </c>
       <c r="CK28" s="39">
-        <f t="shared" ref="CK28" si="135">CK12/CG12-1</f>
+        <f t="shared" ref="CK28" si="137">CK12/CG12-1</f>
         <v>-1</v>
       </c>
       <c r="CL28" s="39">
-        <f t="shared" ref="CL28" si="136">CL12/CH12-1</f>
+        <f t="shared" ref="CL28" si="138">CL12/CH12-1</f>
         <v>-1</v>
       </c>
       <c r="CM28" s="39"/>
@@ -10158,35 +10159,35 @@
         <v>0.31386124896535295</v>
       </c>
       <c r="CV28" s="39">
-        <f t="shared" ref="CV28:DC28" si="137">CV12/CU12-1</f>
+        <f t="shared" ref="CV28:DC28" si="139">CV12/CU12-1</f>
         <v>0.63264638446064292</v>
       </c>
       <c r="CW28" s="39">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>0.16512567258057298</v>
       </c>
       <c r="CX28" s="39">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>0.10335240832420101</v>
       </c>
       <c r="CY28" s="39">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>2.0200387387360186E-2</v>
       </c>
       <c r="CZ28" s="39">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>4.1322994600938134E-2</v>
       </c>
       <c r="DA28" s="39">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>-5.1521438367457706E-2</v>
       </c>
       <c r="DB28" s="39">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>-2.716004370134506E-2</v>
       </c>
       <c r="DC28" s="23">
-        <f t="shared" si="137"/>
+        <f t="shared" si="139"/>
         <v>-0.33650888585226835</v>
       </c>
       <c r="DD28" s="24"/>
@@ -10278,7 +10279,7 @@
       <c r="BN29" s="44"/>
       <c r="BO29" s="41"/>
       <c r="BP29" s="41">
-        <f t="shared" ref="BP29" si="138">BP23/BL23-1</f>
+        <f t="shared" ref="BP29" si="140">BP23/BL23-1</f>
         <v>0.54032957502168322</v>
       </c>
       <c r="BQ29" s="41">
@@ -10294,79 +10295,79 @@
         <v>0.41161290322580668</v>
       </c>
       <c r="BT29" s="41">
-        <f t="shared" ref="BT29:BU29" si="139">BT23/BP23-1</f>
+        <f t="shared" ref="BT29:BU29" si="141">BT23/BP23-1</f>
         <v>-5.5180180180180671E-2</v>
       </c>
       <c r="BU29" s="41">
-        <f t="shared" si="139"/>
+        <f t="shared" si="141"/>
         <v>0.28517722878625107</v>
       </c>
       <c r="BV29" s="41">
-        <f t="shared" ref="BV29" si="140">BV23/BR23-1</f>
+        <f t="shared" ref="BV29" si="142">BV23/BR23-1</f>
         <v>5.4957507082152857E-2</v>
       </c>
       <c r="BW29" s="41">
-        <f t="shared" ref="BW29" si="141">BW23/BS23-1</f>
+        <f t="shared" ref="BW29" si="143">BW23/BS23-1</f>
         <v>0.13528336380255923</v>
       </c>
       <c r="BX29" s="41">
-        <f t="shared" ref="BX29" si="142">BX23/BT23-1</f>
+        <f t="shared" ref="BX29" si="144">BX23/BT23-1</f>
         <v>0.54469606674612581</v>
       </c>
       <c r="BY29" s="41">
-        <f t="shared" ref="BY29" si="143">BY23/BU23-1</f>
+        <f t="shared" ref="BY29" si="145">BY23/BU23-1</f>
         <v>0.11826159632260747</v>
       </c>
       <c r="BZ29" s="41">
-        <f t="shared" ref="BZ29:CD29" si="144">BZ23/BV23-1</f>
+        <f t="shared" ref="BZ29:CD29" si="146">BZ23/BV23-1</f>
         <v>0.16595059076262042</v>
       </c>
       <c r="CA29" s="41">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.23429951690821271</v>
       </c>
       <c r="CB29" s="41">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>7.2916666666667629E-2</v>
       </c>
       <c r="CC29" s="41">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.1550822122571005</v>
       </c>
       <c r="CD29" s="41">
-        <f t="shared" si="144"/>
+        <f t="shared" si="146"/>
         <v>0.55181943804698386</v>
       </c>
       <c r="CE29" s="41">
-        <f t="shared" ref="CE29:CG29" si="145">CE23/CA23-1</f>
+        <f t="shared" ref="CE29:CG29" si="147">CE23/CA23-1</f>
         <v>0.1686236138290933</v>
       </c>
       <c r="CF29" s="41">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>0.32722042430780207</v>
       </c>
       <c r="CG29" s="41">
-        <f t="shared" si="145"/>
+        <f t="shared" si="147"/>
         <v>0.20511161436428327</v>
       </c>
       <c r="CH29" s="41">
-        <f t="shared" ref="CH29" si="146">CH23/CD23-1</f>
+        <f t="shared" ref="CH29" si="148">CH23/CD23-1</f>
         <v>0.11098842386464813</v>
       </c>
       <c r="CI29" s="41">
-        <f t="shared" ref="CI29" si="147">CI23/CE23-1</f>
+        <f t="shared" ref="CI29" si="149">CI23/CE23-1</f>
         <v>-1</v>
       </c>
       <c r="CJ29" s="41">
-        <f t="shared" ref="CJ29" si="148">CJ23/CF23-1</f>
+        <f t="shared" ref="CJ29" si="150">CJ23/CF23-1</f>
         <v>-1</v>
       </c>
       <c r="CK29" s="41">
-        <f t="shared" ref="CK29" si="149">CK23/CG23-1</f>
+        <f t="shared" ref="CK29" si="151">CK23/CG23-1</f>
         <v>-1</v>
       </c>
       <c r="CL29" s="41">
-        <f t="shared" ref="CL29" si="150">CL23/CH23-1</f>
+        <f t="shared" ref="CL29" si="152">CL23/CH23-1</f>
         <v>-1</v>
       </c>
       <c r="CM29" s="41"/>
@@ -10374,59 +10375,59 @@
       <c r="CO29" s="51"/>
       <c r="CP29" s="44"/>
       <c r="CQ29" s="41">
-        <f t="shared" ref="CQ29:DD29" si="151">CQ24/CP24-1</f>
+        <f t="shared" ref="CQ29:DD29" si="153">CQ24/CP24-1</f>
         <v>2.8984620860035641</v>
       </c>
       <c r="CR29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>0.18797872687932204</v>
       </c>
       <c r="CS29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>-0.60165904823049299</v>
       </c>
       <c r="CT29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>0.6597376200962195</v>
       </c>
       <c r="CU29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>-0.51290241653756485</v>
       </c>
       <c r="CV29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>0.91178188779530589</v>
       </c>
       <c r="CW29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>4.1627693604473492E-3</v>
       </c>
       <c r="CX29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>2.1819636178744353</v>
       </c>
       <c r="CY29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>5.8818434765541827E-2</v>
       </c>
       <c r="CZ29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>0.12940806459422127</v>
       </c>
       <c r="DA29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>1.2740331895238599E-2</v>
       </c>
       <c r="DB29" s="41">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>4.2430332899238588E-2</v>
       </c>
       <c r="DC29" s="26">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>-0.27015406811167419</v>
       </c>
       <c r="DD29" s="26">
-        <f t="shared" si="151"/>
+        <f t="shared" si="153"/>
         <v>-0.19428898044874565</v>
       </c>
       <c r="DE29" s="43"/>
@@ -10456,75 +10457,75 @@
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26">
-        <f t="shared" ref="G30:R30" si="152">G3/C3-1</f>
+        <f t="shared" ref="G30:R30" si="154">G3/C3-1</f>
         <v>0.4583740973678081</v>
       </c>
       <c r="H30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.35402024177677816</v>
       </c>
       <c r="I30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.23810283235519258</v>
       </c>
       <c r="J30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.56162009197028651</v>
       </c>
       <c r="K30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.21869409660107331</v>
       </c>
       <c r="L30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.27633013236439141</v>
       </c>
       <c r="M30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.45969549424221356</v>
       </c>
       <c r="N30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.28885314970439668</v>
       </c>
       <c r="O30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.55053735255570113</v>
       </c>
       <c r="P30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.33186245602619113</v>
       </c>
       <c r="Q30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.27334498155697928</v>
       </c>
       <c r="R30" s="26">
-        <f t="shared" si="152"/>
+        <f t="shared" si="154"/>
         <v>0.28538287140371543</v>
       </c>
       <c r="S30" s="26">
-        <f t="shared" ref="S30:X30" si="153">S3/O3-1</f>
+        <f t="shared" ref="S30:X30" si="155">S3/O3-1</f>
         <v>0.2993085726843947</v>
       </c>
       <c r="T30" s="26">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>0.23683527489808687</v>
       </c>
       <c r="U30" s="26">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>0.21138200113653705</v>
       </c>
       <c r="V30" s="26">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>0.18154969440912261</v>
       </c>
       <c r="W30" s="26">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>0.2460511592807515</v>
       </c>
       <c r="X30" s="26">
-        <f t="shared" si="153"/>
+        <f t="shared" si="155"/>
         <v>0.18958387339678318</v>
       </c>
       <c r="Y30" s="26">
@@ -10577,95 +10578,95 @@
       <c r="BN30" s="41"/>
       <c r="BO30" s="41"/>
       <c r="BP30" s="41">
-        <f t="shared" ref="BP30" si="154">BP3/BL3-1</f>
+        <f t="shared" ref="BP30" si="156">BP3/BL3-1</f>
         <v>0.1747899159663866</v>
       </c>
       <c r="BQ30" s="41">
-        <f t="shared" ref="BQ30:CD30" si="155">BQ3/BM3-1</f>
+        <f t="shared" ref="BQ30:CD30" si="157">BQ3/BM3-1</f>
         <v>7.2289156626506035E-3</v>
       </c>
       <c r="BR30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-7.5058639562157969E-2</v>
       </c>
       <c r="BS30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>1.1520737327188835E-2</v>
       </c>
       <c r="BT30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-5.5793991416309141E-2</v>
       </c>
       <c r="BU30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-9.0909090909090939E-2</v>
       </c>
       <c r="BV30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>3.5502958579881616E-2</v>
       </c>
       <c r="BW30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-7.8208048595292179E-2</v>
       </c>
       <c r="BX30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-3.6363636363636376E-2</v>
       </c>
       <c r="BY30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="BZ30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-6.0408163265306181E-2</v>
       </c>
       <c r="CA30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>5.4365733113673764E-2</v>
       </c>
       <c r="CB30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>0.15801886792452846</v>
       </c>
       <c r="CC30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>-2.1357742181540629E-2</v>
       </c>
       <c r="CD30" s="41">
-        <f t="shared" si="155"/>
+        <f t="shared" si="157"/>
         <v>0.16854908774978283</v>
       </c>
       <c r="CE30" s="41">
-        <f t="shared" ref="CE30:CG30" si="156">CE3/CA3-1</f>
+        <f t="shared" ref="CE30:CG30" si="158">CE3/CA3-1</f>
         <v>7.9687499999999911E-2</v>
       </c>
       <c r="CF30" s="41">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>-8.5539714867617245E-2</v>
       </c>
       <c r="CG30" s="41">
-        <f t="shared" si="156"/>
+        <f t="shared" si="158"/>
         <v>-1.8706157443491911E-2</v>
       </c>
       <c r="CH30" s="41">
-        <f t="shared" ref="CH30" si="157">CH3/CD3-1</f>
+        <f t="shared" ref="CH30" si="159">CH3/CD3-1</f>
         <v>-6.394052044609666E-2</v>
       </c>
       <c r="CI30" s="41">
-        <f t="shared" ref="CI30" si="158">CI3/CE3-1</f>
+        <f t="shared" ref="CI30" si="160">CI3/CE3-1</f>
         <v>-1</v>
       </c>
       <c r="CJ30" s="41">
-        <f t="shared" ref="CJ30" si="159">CJ3/CF3-1</f>
+        <f t="shared" ref="CJ30" si="161">CJ3/CF3-1</f>
         <v>-1</v>
       </c>
       <c r="CK30" s="41">
-        <f t="shared" ref="CK30" si="160">CK3/CG3-1</f>
+        <f t="shared" ref="CK30" si="162">CK3/CG3-1</f>
         <v>-1</v>
       </c>
       <c r="CL30" s="41">
-        <f t="shared" ref="CL30" si="161">CL3/CH3-1</f>
+        <f t="shared" ref="CL30" si="163">CL3/CH3-1</f>
         <v>-1</v>
       </c>
       <c r="CM30" s="41"/>
@@ -10673,27 +10674,27 @@
       <c r="CO30" s="52"/>
       <c r="CP30" s="41"/>
       <c r="CQ30" s="41">
-        <f t="shared" ref="CQ30:CV30" si="162">CQ3/CP3-1</f>
+        <f t="shared" ref="CQ30:CV30" si="164">CQ3/CP3-1</f>
         <v>0.65315669947009858</v>
       </c>
       <c r="CR30" s="41">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>0.39643377201417707</v>
       </c>
       <c r="CS30" s="41">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>0.3174818662364407</v>
       </c>
       <c r="CT30" s="41">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>0.34372059914280184</v>
       </c>
       <c r="CU30" s="41">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>0.22874310947780208</v>
       </c>
       <c r="CV30" s="41">
-        <f t="shared" si="162"/>
+        <f t="shared" si="164"/>
         <v>0.21682213686603435</v>
       </c>
       <c r="CW30" s="41">
@@ -10813,95 +10814,95 @@
       <c r="BN31" s="39"/>
       <c r="BO31" s="39"/>
       <c r="BP31" s="39">
-        <f t="shared" ref="BP31" si="163">BP5/BL5-1</f>
+        <f t="shared" ref="BP31" si="165">BP5/BL5-1</f>
         <v>0.29026845637583909</v>
       </c>
       <c r="BQ31" s="39">
-        <f t="shared" ref="BQ31:BS31" si="164">BQ5/BM5-1</f>
+        <f t="shared" ref="BQ31:BS31" si="166">BQ5/BM5-1</f>
         <v>0.26795366795366782</v>
       </c>
       <c r="BR31" s="39">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>0.26423690205011408</v>
       </c>
       <c r="BS31" s="39">
-        <f t="shared" si="164"/>
+        <f t="shared" si="166"/>
         <v>0.39837398373983746</v>
       </c>
       <c r="BT31" s="39">
-        <f t="shared" ref="BT31" si="165">BT5/BP5-1</f>
+        <f t="shared" ref="BT31" si="167">BT5/BP5-1</f>
         <v>0.30689206762028598</v>
       </c>
       <c r="BU31" s="39">
-        <f t="shared" ref="BU31" si="166">BU5/BQ5-1</f>
+        <f t="shared" ref="BU31" si="168">BU5/BQ5-1</f>
         <v>0.56942752740560287</v>
       </c>
       <c r="BV31" s="39">
-        <f t="shared" ref="BV31" si="167">BV5/BR5-1</f>
+        <f t="shared" ref="BV31" si="169">BV5/BR5-1</f>
         <v>0.45525525525525534</v>
       </c>
       <c r="BW31" s="39">
-        <f t="shared" ref="BW31" si="168">BW5/BS5-1</f>
+        <f t="shared" ref="BW31" si="170">BW5/BS5-1</f>
         <v>0.38604651162790704</v>
       </c>
       <c r="BX31" s="39">
-        <f t="shared" ref="BX31" si="169">BX5/BT5-1</f>
+        <f t="shared" ref="BX31" si="171">BX5/BT5-1</f>
         <v>0.58656716417910437</v>
       </c>
       <c r="BY31" s="39">
-        <f t="shared" ref="BY31" si="170">BY5/BU5-1</f>
+        <f t="shared" ref="BY31" si="172">BY5/BU5-1</f>
         <v>-0.53162592161428013</v>
       </c>
       <c r="BZ31" s="39">
-        <f t="shared" ref="BZ31:CD31" si="171">BZ5/BV5-1</f>
+        <f t="shared" ref="BZ31:CD31" si="173">BZ5/BV5-1</f>
         <v>-0.43499793644242679</v>
       </c>
       <c r="CA31" s="39">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>-0.39177852348993292</v>
       </c>
       <c r="CB31" s="39">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>-0.56130448416431478</v>
       </c>
       <c r="CC31" s="39">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>0.31897265948632958</v>
       </c>
       <c r="CD31" s="39">
-        <f t="shared" si="171"/>
+        <f t="shared" si="173"/>
         <v>4.2366691015339519E-2</v>
       </c>
       <c r="CE31" s="39">
-        <f t="shared" ref="CE31:CG31" si="172">CE5/CA5-1</f>
+        <f t="shared" ref="CE31:CG31" si="174">CE5/CA5-1</f>
         <v>0.1296551724137931</v>
       </c>
       <c r="CF31" s="39">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>0.10364546104360262</v>
       </c>
       <c r="CG31" s="39">
-        <f t="shared" si="172"/>
+        <f t="shared" si="174"/>
         <v>-0.10929648241206014</v>
       </c>
       <c r="CH31" s="39">
-        <f t="shared" ref="CH31" si="173">CH5/CD5-1</f>
+        <f t="shared" ref="CH31" si="175">CH5/CD5-1</f>
         <v>-6.3069376313943382E-3</v>
       </c>
       <c r="CI31" s="39">
-        <f t="shared" ref="CI31" si="174">CI5/CE5-1</f>
+        <f t="shared" ref="CI31" si="176">CI5/CE5-1</f>
         <v>-1</v>
       </c>
       <c r="CJ31" s="39">
-        <f t="shared" ref="CJ31" si="175">CJ5/CF5-1</f>
+        <f t="shared" ref="CJ31" si="177">CJ5/CF5-1</f>
         <v>-1</v>
       </c>
       <c r="CK31" s="39">
-        <f t="shared" ref="CK31" si="176">CK5/CG5-1</f>
+        <f t="shared" ref="CK31" si="178">CK5/CG5-1</f>
         <v>-1</v>
       </c>
       <c r="CL31" s="39">
-        <f t="shared" ref="CL31" si="177">CL5/CH5-1</f>
+        <f t="shared" ref="CL31" si="179">CL5/CH5-1</f>
         <v>-1</v>
       </c>
       <c r="CM31" s="39"/>
@@ -11080,7 +11081,7 @@
       <c r="DX32" s="3"/>
       <c r="DY32" s="18">
         <f>DY31/Main!K3</f>
-        <v>285.81610717586545</v>
+        <v>316.47564106442951</v>
       </c>
     </row>
     <row r="33" spans="2:121" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -11089,79 +11090,79 @@
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17">
-        <f t="shared" ref="D33:L33" si="178">D3/C3-1</f>
+        <f t="shared" ref="D33:L33" si="180">D3/C3-1</f>
         <v>0.32569298858607043</v>
       </c>
       <c r="E33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>0.10177115546809112</v>
       </c>
       <c r="F33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>-9.830313855575401E-2</v>
       </c>
       <c r="G33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>0.10732224973470106</v>
       </c>
       <c r="H33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>0.23083312036800407</v>
       </c>
       <c r="I33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>7.4487412405916942E-3</v>
       </c>
       <c r="J33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>0.13731097199680553</v>
       </c>
       <c r="K33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>-0.13584162004213196</v>
       </c>
       <c r="L33" s="17">
-        <f t="shared" si="178"/>
+        <f t="shared" si="180"/>
         <v>0.2890432503276541</v>
       </c>
       <c r="M33" s="17">
-        <f t="shared" ref="M33:V33" si="179">M3/L3-1</f>
+        <f t="shared" ref="M33:V33" si="181">M3/L3-1</f>
         <v>0.15218496451593233</v>
       </c>
       <c r="N33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>4.2004200420042714E-3</v>
       </c>
       <c r="O33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>3.9614052971054026E-2</v>
       </c>
       <c r="P33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>0.10724730782885072</v>
       </c>
       <c r="Q33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>0.10156190359863815</v>
       </c>
       <c r="R33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>1.3693883491108672E-2</v>
       </c>
       <c r="S33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>5.0877121019456739E-2</v>
       </c>
       <c r="T33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>5.4008691352884552E-2</v>
       </c>
       <c r="U33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>7.8892468738041455E-2</v>
       </c>
       <c r="V33" s="17">
-        <f t="shared" si="179"/>
+        <f t="shared" si="181"/>
         <v>-1.127002288329515E-2</v>
       </c>
       <c r="W33" s="17">
@@ -11279,43 +11280,43 @@
         <v>15</v>
       </c>
       <c r="C34" s="17">
-        <f t="shared" ref="C34:S34" si="180">C14/C12</f>
+        <f t="shared" ref="C34:S34" si="182">C14/C12</f>
         <v>0.88990390830352906</v>
       </c>
       <c r="D34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89436736866620092</v>
       </c>
       <c r="E34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.8960315056043624</v>
       </c>
       <c r="F34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89362707061165281</v>
       </c>
       <c r="G34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.88309612833192619</v>
       </c>
       <c r="H34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89454590632376696</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89717058197390909</v>
       </c>
       <c r="J34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89628158687208137</v>
       </c>
       <c r="K34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89056237396997684</v>
       </c>
       <c r="L34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89693426713742741</v>
       </c>
       <c r="M34" s="17">
@@ -11327,43 +11328,43 @@
         <v>0.89386957828308122</v>
       </c>
       <c r="O34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.88901961416345665</v>
       </c>
       <c r="P34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89305093646070366</v>
       </c>
       <c r="Q34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89683068557415502</v>
       </c>
       <c r="R34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.89314808468007711</v>
       </c>
       <c r="S34" s="17">
-        <f t="shared" si="180"/>
+        <f t="shared" si="182"/>
         <v>0.88729461934027343</v>
       </c>
       <c r="T34" s="17">
-        <f t="shared" ref="T34:Z34" si="181">T14/T12</f>
+        <f t="shared" ref="T34:Z34" si="183">T14/T12</f>
         <v>0.90853774708263879</v>
       </c>
       <c r="U34" s="17">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.86879596770045775</v>
       </c>
       <c r="V34" s="17">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.87618776566932599</v>
       </c>
       <c r="W34" s="17">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.88449720670391063</v>
       </c>
       <c r="X34" s="17">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.87865387552639818</v>
       </c>
       <c r="Y34" s="17">
@@ -11371,7 +11372,7 @@
         <v>0.87295813034044312</v>
       </c>
       <c r="Z34" s="17">
-        <f t="shared" si="181"/>
+        <f t="shared" si="183"/>
         <v>0.88865729199829402</v>
       </c>
       <c r="AA34" s="17">
@@ -11422,23 +11423,23 @@
       <c r="BL34" s="40"/>
       <c r="BM34" s="40"/>
       <c r="BN34" s="40">
-        <f t="shared" ref="BN34:BR34" si="182">BN14/BN12</f>
+        <f t="shared" ref="BN34:BR34" si="184">BN14/BN12</f>
         <v>0.9095869056897895</v>
       </c>
       <c r="BO34" s="40">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>0.93932999208652068</v>
       </c>
       <c r="BP34" s="40">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>0.9166853303471445</v>
       </c>
       <c r="BQ34" s="40">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>0.93771081628063868</v>
       </c>
       <c r="BR34" s="40">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="BS34" s="40">
@@ -11446,79 +11447,79 @@
         <v>0.94392725698203084</v>
       </c>
       <c r="BT34" s="40">
-        <f t="shared" ref="BT34:BU34" si="183">BT14/BT12</f>
+        <f t="shared" ref="BT34:BU34" si="185">BT14/BT12</f>
         <v>0.93638894838295139</v>
       </c>
       <c r="BU34" s="40">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>0.9279069767441861</v>
       </c>
       <c r="BV34" s="40">
-        <f t="shared" ref="BV34:CG34" si="184">BV14/BV12</f>
+        <f t="shared" ref="BV34:CG34" si="186">BV14/BV12</f>
         <v>0.88036622583926749</v>
       </c>
       <c r="BW34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.89682383113040043</v>
       </c>
       <c r="BX34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.89253981559094708</v>
       </c>
       <c r="BY34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.88496882179192649</v>
       </c>
       <c r="BZ34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.88449650235887423</v>
       </c>
       <c r="CA34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.89243027888446225</v>
       </c>
       <c r="CB34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.89117359071198776</v>
       </c>
       <c r="CC34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.88903725464013883</v>
       </c>
       <c r="CD34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.89835575485799712</v>
       </c>
       <c r="CE34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.88469284994964748</v>
       </c>
       <c r="CF34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.89156023040320553</v>
       </c>
       <c r="CG34" s="40">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>0.8749218261413384</v>
       </c>
       <c r="CH34" s="40">
-        <f t="shared" ref="CH34:CL34" si="185">CH14/CH12</f>
+        <f t="shared" ref="CH34:CL34" si="187">CH14/CH12</f>
         <v>0.87</v>
       </c>
       <c r="CI34" s="40" t="e">
-        <f t="shared" si="185"/>
+        <f t="shared" si="187"/>
         <v>#DIV/0!</v>
       </c>
       <c r="CJ34" s="40" t="e">
-        <f t="shared" si="185"/>
+        <f t="shared" si="187"/>
         <v>#DIV/0!</v>
       </c>
       <c r="CK34" s="40" t="e">
-        <f t="shared" si="185"/>
+        <f t="shared" si="187"/>
         <v>#DIV/0!</v>
       </c>
       <c r="CL34" s="40" t="e">
-        <f t="shared" si="185"/>
+        <f t="shared" si="187"/>
         <v>#DIV/0!</v>
       </c>
       <c r="CM34" s="40"/>
@@ -11594,47 +11595,47 @@
         <v>16</v>
       </c>
       <c r="C35" s="17">
-        <f t="shared" ref="C35:M35" si="186">C15/C12</f>
+        <f t="shared" ref="C35:M35" si="188">C15/C12</f>
         <v>0.23010298616796659</v>
       </c>
       <c r="D35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.23372259373856338</v>
       </c>
       <c r="E35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.17025143895789155</v>
       </c>
       <c r="F35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.22502614621638947</v>
       </c>
       <c r="G35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.36494391508865043</v>
       </c>
       <c r="H35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.2949683190458442</v>
       </c>
       <c r="I35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.3191078545436542</v>
       </c>
       <c r="J35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.41869244533670846</v>
       </c>
       <c r="K35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.37750504120092604</v>
       </c>
       <c r="L35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.39501456657212863</v>
       </c>
       <c r="M35" s="17">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.32454907274112965</v>
       </c>
       <c r="N35" s="17">
@@ -11642,35 +11643,35 @@
         <v>0.73835520384653919</v>
       </c>
       <c r="O35" s="17">
-        <f t="shared" ref="O35:V35" si="187">O15/O12</f>
+        <f t="shared" ref="O35:V35" si="189">O15/O12</f>
         <v>0.31155414443889312</v>
       </c>
       <c r="P35" s="17">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.27364490343660652</v>
       </c>
       <c r="Q35" s="17">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.40006930376372751</v>
       </c>
       <c r="R35" s="17">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.28822071656428772</v>
       </c>
       <c r="S35" s="17">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.3664618086040386</v>
       </c>
       <c r="T35" s="17">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.28588949749940468</v>
       </c>
       <c r="U35" s="17">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.42351488967751888</v>
       </c>
       <c r="V35" s="17">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>0.51942197699292147</v>
       </c>
       <c r="W35" s="17">
@@ -11812,47 +11813,47 @@
         <v>17</v>
       </c>
       <c r="C36" s="17">
-        <f t="shared" ref="C36:M36" si="188">C16/C12</f>
+        <f t="shared" ref="C36:M36" si="190">C16/C12</f>
         <v>0.3651053561425433</v>
       </c>
       <c r="D36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.28925042419403135</v>
       </c>
       <c r="E36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.28545895183277797</v>
       </c>
       <c r="F36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.31925373637866467</v>
       </c>
       <c r="G36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.44325171873115432</v>
       </c>
       <c r="H36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.31343023978133927</v>
       </c>
       <c r="I36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.29504666188083273</v>
       </c>
       <c r="J36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.40014402304368696</v>
       </c>
       <c r="K36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.42572630635564734</v>
       </c>
       <c r="L36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.34670371013486134</v>
       </c>
       <c r="M36" s="17">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>0.33125582183080704</v>
       </c>
       <c r="N36" s="17">
@@ -11860,35 +11861,35 @@
         <v>0.29566930448429002</v>
       </c>
       <c r="O36" s="17">
-        <f t="shared" ref="O36:V36" si="189">O16/O12</f>
+        <f t="shared" ref="O36:V36" si="191">O16/O12</f>
         <v>0.3396779860428385</v>
       </c>
       <c r="P36" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>0.23087694731314543</v>
       </c>
       <c r="Q36" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>0.25606407932615421</v>
       </c>
       <c r="R36" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>0.35262713875194435</v>
       </c>
       <c r="S36" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>0.2628747021196538</v>
       </c>
       <c r="T36" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>0.23473446058585382</v>
       </c>
       <c r="U36" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>0.32454868075914206</v>
       </c>
       <c r="V36" s="17">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>0.37670648072491569</v>
       </c>
       <c r="W36" s="17">
@@ -12030,43 +12031,43 @@
         <v>18</v>
       </c>
       <c r="C37" s="17">
-        <f t="shared" ref="C37:R37" si="190">C22/C21</f>
+        <f t="shared" ref="C37:R37" si="192">C22/C21</f>
         <v>0</v>
       </c>
       <c r="D37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="E37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0</v>
       </c>
       <c r="F37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>-1.4681101040617657</v>
       </c>
       <c r="G37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.44874551971326215</v>
       </c>
       <c r="H37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.49753694581280761</v>
       </c>
       <c r="I37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.39872340425531894</v>
       </c>
       <c r="J37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>-6.1255455712451869</v>
       </c>
       <c r="K37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.21290702814203619</v>
       </c>
       <c r="L37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.34851885098743257</v>
       </c>
       <c r="M37" s="17">
@@ -12078,43 +12079,43 @@
         <v>1.3880422039859313</v>
       </c>
       <c r="O37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.36498301498023061</v>
       </c>
       <c r="P37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.27262196332825839</v>
       </c>
       <c r="Q37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.36500830021630881</v>
       </c>
       <c r="R37" s="17">
-        <f t="shared" si="190"/>
+        <f t="shared" si="192"/>
         <v>0.35</v>
       </c>
       <c r="S37" s="17">
-        <f t="shared" ref="S37:X37" si="191">S22/S21</f>
+        <f t="shared" ref="S37:X37" si="193">S22/S21</f>
         <v>0.34001800360072021</v>
       </c>
       <c r="T37" s="17">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>5.6274162137022958E-2</v>
       </c>
       <c r="U37" s="17">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>-0.30460436202718338</v>
       </c>
       <c r="V37" s="17">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>-0.29071694985495339</v>
       </c>
       <c r="W37" s="17">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>0.34001603849238149</v>
       </c>
       <c r="X37" s="17">
-        <f t="shared" si="191"/>
+        <f t="shared" si="193"/>
         <v>0.33753228271754576</v>
       </c>
       <c r="Y37" s="17">
@@ -12407,31 +12408,31 @@
       <c r="Q39" s="16"/>
       <c r="R39" s="16"/>
       <c r="S39" s="16">
-        <f t="shared" ref="S39:Y39" si="192">+S42-S57</f>
+        <f t="shared" ref="S39:Y39" si="194">+S42-S57</f>
         <v>156.07499999999999</v>
       </c>
       <c r="T39" s="16">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>183.98599999999999</v>
       </c>
       <c r="U39" s="16">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>188.27100000000004</v>
       </c>
       <c r="V39" s="16">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>197.82400000000001</v>
       </c>
       <c r="W39" s="16">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>270.03999999999996</v>
       </c>
       <c r="X39" s="16">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>326.96899999999994</v>
       </c>
       <c r="Y39" s="16">
-        <f t="shared" si="192"/>
+        <f t="shared" si="194"/>
         <v>434.245</v>
       </c>
       <c r="Z39" s="16">
@@ -12522,35 +12523,35 @@
         <v>443.78900000000004</v>
       </c>
       <c r="CW39" s="35">
-        <f t="shared" ref="CW39:DD39" si="193">+CV39+CW23</f>
+        <f t="shared" ref="CW39:DD39" si="195">+CV39+CW23</f>
         <v>550.89230800000007</v>
       </c>
       <c r="CX39" s="35">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>891.69113741000001</v>
       </c>
       <c r="CY39" s="35">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>1252.5352205358249</v>
       </c>
       <c r="CZ39" s="35">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>1660.0754380792391</v>
       </c>
       <c r="DA39" s="35">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>2072.8078532548143</v>
       </c>
       <c r="DB39" s="35">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>2503.0526422045959</v>
       </c>
       <c r="DC39" s="16">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>2817.0650511357453</v>
       </c>
       <c r="DD39" s="16">
-        <f t="shared" si="193"/>
+        <f t="shared" si="195"/>
         <v>3070.0683092874069</v>
       </c>
       <c r="DE39" s="16"/>
@@ -12589,31 +12590,31 @@
       <c r="R40" s="16"/>
       <c r="S40" s="16"/>
       <c r="T40" s="16">
-        <f t="shared" ref="T40:Z40" si="194">+T39-S39</f>
+        <f t="shared" ref="T40:Z40" si="196">+T39-S39</f>
         <v>27.911000000000001</v>
       </c>
       <c r="U40" s="16">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>4.2850000000000534</v>
       </c>
       <c r="V40" s="16">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>9.5529999999999688</v>
       </c>
       <c r="W40" s="16">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>72.215999999999951</v>
       </c>
       <c r="X40" s="16">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>56.928999999999974</v>
       </c>
       <c r="Y40" s="16">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>107.27600000000007</v>
       </c>
       <c r="Z40" s="16">
-        <f t="shared" si="194"/>
+        <f t="shared" si="196"/>
         <v>9.5440000000000396</v>
       </c>
       <c r="AA40" s="16"/>
@@ -12966,7 +12967,7 @@
       <c r="CT42" s="35"/>
       <c r="CU42" s="35"/>
       <c r="CV42" s="35">
-        <f t="shared" ref="CV42:CV52" si="195">Z42</f>
+        <f t="shared" ref="CV42:CV52" si="197">Z42</f>
         <v>765.05399999999997</v>
       </c>
       <c r="CW42" s="35"/>
@@ -13113,7 +13114,7 @@
       <c r="CT43" s="35"/>
       <c r="CU43" s="35"/>
       <c r="CV43" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>73.706999999999994</v>
       </c>
       <c r="CW43" s="35"/>
@@ -13261,7 +13262,7 @@
       <c r="CT44" s="35"/>
       <c r="CU44" s="35"/>
       <c r="CV44" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>6.84</v>
       </c>
       <c r="CW44" s="35"/>
@@ -13406,7 +13407,7 @@
       <c r="CT45" s="35"/>
       <c r="CU45" s="35"/>
       <c r="CV45" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>8.7520000000000007</v>
       </c>
       <c r="CW45" s="35"/>
@@ -13553,7 +13554,7 @@
       <c r="CT46" s="35"/>
       <c r="CU46" s="35"/>
       <c r="CV46" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>35.520000000000003</v>
       </c>
       <c r="CW46" s="35"/>
@@ -13700,7 +13701,7 @@
       <c r="CT47" s="35"/>
       <c r="CU47" s="35"/>
       <c r="CV47" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>12.585000000000001</v>
       </c>
       <c r="CW47" s="35"/>
@@ -13848,7 +13849,7 @@
       <c r="CT48" s="35"/>
       <c r="CU48" s="35"/>
       <c r="CV48" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>9.8610000000000007</v>
       </c>
       <c r="CW48" s="35"/>
@@ -13996,7 +13997,7 @@
       <c r="CT49" s="35"/>
       <c r="CU49" s="35"/>
       <c r="CV49" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>306.04399999999998</v>
       </c>
       <c r="CW49" s="35"/>
@@ -14141,7 +14142,7 @@
       <c r="CT50" s="35"/>
       <c r="CU50" s="35"/>
       <c r="CV50" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>202.13499999999999</v>
       </c>
       <c r="CW50" s="35"/>
@@ -14279,7 +14280,7 @@
       <c r="CT51" s="35"/>
       <c r="CU51" s="35"/>
       <c r="CV51" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>11.137</v>
       </c>
       <c r="CW51" s="35"/>
@@ -14316,35 +14317,35 @@
       <c r="Q52" s="16"/>
       <c r="R52" s="16"/>
       <c r="S52" s="16">
-        <f t="shared" ref="S52:Z52" si="196">SUM(S42:S51)</f>
+        <f t="shared" ref="S52:Z52" si="198">SUM(S42:S51)</f>
         <v>902.81299999999999</v>
       </c>
       <c r="T52" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>951.67099999999994</v>
       </c>
       <c r="U52" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>1004.727</v>
       </c>
       <c r="V52" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>1051.5439999999999</v>
       </c>
       <c r="W52" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>1126.703</v>
       </c>
       <c r="X52" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>1187.6750000000002</v>
       </c>
       <c r="Y52" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>1282.7840000000001</v>
       </c>
       <c r="Z52" s="16">
-        <f t="shared" si="196"/>
+        <f t="shared" si="198"/>
         <v>1431.6349999999998</v>
       </c>
       <c r="AA52" s="16"/>
@@ -14427,7 +14428,7 @@
       <c r="CT52" s="35"/>
       <c r="CU52" s="35"/>
       <c r="CV52" s="35">
-        <f t="shared" si="195"/>
+        <f t="shared" si="197"/>
         <v>1431.6349999999998</v>
       </c>
       <c r="CW52" s="35"/>
@@ -15066,7 +15067,7 @@
       <c r="CT57" s="35"/>
       <c r="CU57" s="35"/>
       <c r="CV57" s="35">
-        <f t="shared" ref="CV57:CV62" si="197">Z57</f>
+        <f t="shared" ref="CV57:CV62" si="199">Z57</f>
         <v>235.96799999999999</v>
       </c>
       <c r="CW57" s="35"/>
@@ -15203,7 +15204,7 @@
       <c r="CT58" s="35"/>
       <c r="CU58" s="35"/>
       <c r="CV58" s="35">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>68.929000000000002</v>
       </c>
       <c r="CW58" s="35"/>
@@ -15351,7 +15352,7 @@
       <c r="CT59" s="35"/>
       <c r="CU59" s="35"/>
       <c r="CV59" s="35">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>176.42600000000002</v>
       </c>
       <c r="CW59" s="35"/>
@@ -15388,35 +15389,35 @@
       <c r="Q60" s="16"/>
       <c r="R60" s="16"/>
       <c r="S60" s="16">
-        <f t="shared" ref="S60:Z60" si="198">SUM(S54:S59)</f>
+        <f t="shared" ref="S60:Z60" si="200">SUM(S54:S59)</f>
         <v>314.64900000000006</v>
       </c>
       <c r="T60" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>335.80899999999997</v>
       </c>
       <c r="U60" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>354.28800000000001</v>
       </c>
       <c r="V60" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>387.65300000000002</v>
       </c>
       <c r="W60" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>387.57299999999998</v>
       </c>
       <c r="X60" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>394.49199999999996</v>
       </c>
       <c r="Y60" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>431.17099999999999</v>
       </c>
       <c r="Z60" s="16">
-        <f t="shared" si="198"/>
+        <f t="shared" si="200"/>
         <v>547.74900000000002</v>
       </c>
       <c r="AA60" s="16"/>
@@ -15493,7 +15494,7 @@
       <c r="CT60" s="35"/>
       <c r="CU60" s="35"/>
       <c r="CV60" s="35">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>547.74900000000002</v>
       </c>
       <c r="CW60" s="35"/>
@@ -15637,7 +15638,7 @@
       <c r="CT61" s="35"/>
       <c r="CU61" s="35"/>
       <c r="CV61" s="35">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>883.88599999999997</v>
       </c>
       <c r="CW61" s="35"/>
@@ -15674,35 +15675,35 @@
       <c r="Q62" s="16"/>
       <c r="R62" s="16"/>
       <c r="S62" s="16">
-        <f t="shared" ref="S62:Z62" si="199">S61+S60</f>
+        <f t="shared" ref="S62:Z62" si="201">S61+S60</f>
         <v>902.8130000000001</v>
       </c>
       <c r="T62" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>951.67099999999994</v>
       </c>
       <c r="U62" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>1004.727</v>
       </c>
       <c r="V62" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>1051.5439999999999</v>
       </c>
       <c r="W62" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>1126.703</v>
       </c>
       <c r="X62" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>1187.675</v>
       </c>
       <c r="Y62" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>1271.902</v>
       </c>
       <c r="Z62" s="16">
-        <f t="shared" si="199"/>
+        <f t="shared" si="201"/>
         <v>1431.635</v>
       </c>
       <c r="AA62" s="16"/>
@@ -15785,7 +15786,7 @@
       <c r="CT62" s="35"/>
       <c r="CU62" s="35"/>
       <c r="CV62" s="35">
-        <f t="shared" si="197"/>
+        <f t="shared" si="199"/>
         <v>1431.635</v>
       </c>
       <c r="CW62" s="35"/>
@@ -16197,35 +16198,35 @@
       <c r="Q67" s="16"/>
       <c r="R67" s="16"/>
       <c r="S67" s="16">
-        <f t="shared" ref="S67:Z67" si="200">+S23</f>
+        <f t="shared" ref="S67:Z67" si="202">+S23</f>
         <v>13.196999999999999</v>
       </c>
       <c r="T67" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>32.466999999999985</v>
       </c>
       <c r="U67" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>12.382000000000009</v>
       </c>
       <c r="V67" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>-6.2289999999999832</v>
       </c>
       <c r="W67" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>18.929000000000023</v>
       </c>
       <c r="X67" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>37.707000000000036</v>
       </c>
       <c r="Y67" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>39.735999999999976</v>
       </c>
       <c r="Z67" s="16">
-        <f t="shared" si="200"/>
+        <f t="shared" si="202"/>
         <v>9.5440000000000165</v>
       </c>
       <c r="AA67" s="16"/>
@@ -16505,7 +16506,7 @@
         <v>5.0279999999999987</v>
       </c>
       <c r="Z69" s="16">
-        <f t="shared" ref="Z69:Z85" si="201">CV69-SUM(W69:Y69)</f>
+        <f t="shared" ref="Z69:Z85" si="203">CV69-SUM(W69:Y69)</f>
         <v>3.7390000000000025</v>
       </c>
       <c r="AA69" s="16"/>
@@ -16644,7 +16645,7 @@
         <v>1.016</v>
       </c>
       <c r="Z70" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>0.55400000000000027</v>
       </c>
       <c r="AA70" s="16"/>
@@ -16783,7 +16784,7 @@
         <v>17.998000000000005</v>
       </c>
       <c r="Z71" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>-5.0390000000000015</v>
       </c>
       <c r="AA71" s="16"/>
@@ -16922,7 +16923,7 @@
         <v>31.372</v>
       </c>
       <c r="Z72" s="20">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>52.814999999999998</v>
       </c>
       <c r="AA72" s="20"/>
@@ -17058,7 +17059,7 @@
         <v>0</v>
       </c>
       <c r="Z73" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>7.6879999999999997</v>
       </c>
       <c r="AA73" s="16"/>
@@ -17197,7 +17198,7 @@
         <v>4.246999999999999</v>
       </c>
       <c r="Z74" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>-9.9459999999999997</v>
       </c>
       <c r="AA74" s="16"/>
@@ -17336,7 +17337,7 @@
         <v>0.58900000000000008</v>
       </c>
       <c r="Z75" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>15.373999999999999</v>
       </c>
       <c r="AA75" s="16"/>
@@ -17475,7 +17476,7 @@
         <v>-0.49199999999999999</v>
       </c>
       <c r="Z76" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>1.5150000000000001</v>
       </c>
       <c r="AA76" s="16"/>
@@ -17614,7 +17615,7 @@
         <v>-2.3709999999999987</v>
       </c>
       <c r="Z77" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>-5.1000000000000014</v>
       </c>
       <c r="AA77" s="16"/>
@@ -17751,7 +17752,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>0</v>
       </c>
       <c r="AA78" s="16"/>
@@ -17890,7 +17891,7 @@
         <v>7.6560000000000041</v>
       </c>
       <c r="Z79" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>1.8609999999999935</v>
       </c>
       <c r="AA79" s="16"/>
@@ -18029,7 +18030,7 @@
         <v>-2.9940000000000002</v>
       </c>
       <c r="Z80" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>-1.4450000000000003</v>
       </c>
       <c r="AA80" s="16"/>
@@ -18168,7 +18169,7 @@
         <v>1.6500000000000001</v>
       </c>
       <c r="Z81" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>-1.0940000000000001</v>
       </c>
       <c r="AA81" s="16"/>
@@ -18307,7 +18308,7 @@
         <v>-2.4899999999999998</v>
       </c>
       <c r="Z82" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>-1.8050000000000002</v>
       </c>
       <c r="AA82" s="16"/>
@@ -18446,7 +18447,7 @@
         <v>1.8780000000000019</v>
       </c>
       <c r="Z83" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>4.7169999999999987</v>
       </c>
       <c r="AA83" s="16"/>
@@ -18585,7 +18586,7 @@
         <v>3.641999999999999</v>
       </c>
       <c r="Z84" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>10.284999999999998</v>
       </c>
       <c r="AA84" s="16"/>
@@ -18724,7 +18725,7 @@
         <v>-4.7330000000000014</v>
       </c>
       <c r="Z85" s="16">
-        <f t="shared" si="201"/>
+        <f t="shared" si="203"/>
         <v>-43.314999999999998</v>
       </c>
       <c r="AA85" s="16"/>
@@ -18837,35 +18838,35 @@
       <c r="Q86" s="16"/>
       <c r="R86" s="16"/>
       <c r="S86" s="16">
-        <f t="shared" ref="S86:Z86" si="202">SUM(S68:S85)</f>
+        <f t="shared" ref="S86:Z86" si="204">SUM(S68:S85)</f>
         <v>1.3020000000000076</v>
       </c>
       <c r="T86" s="16">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>56.350999999999999</v>
       </c>
       <c r="U86" s="16">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>15.98800000000001</v>
       </c>
       <c r="V86" s="16">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>23.983000000000001</v>
       </c>
       <c r="W86" s="16">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>34.219000000000001</v>
       </c>
       <c r="X86" s="16">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>35.233000000000011</v>
       </c>
       <c r="Y86" s="16">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>101.732</v>
       </c>
       <c r="Z86" s="16">
-        <f t="shared" si="202"/>
+        <f t="shared" si="204"/>
         <v>40.347999999999999</v>
       </c>
       <c r="AA86" s="16"/>
@@ -19001,27 +19002,27 @@
         <v>173</v>
       </c>
       <c r="S88" s="16">
-        <f t="shared" ref="S88:X88" si="203">+S86-S87</f>
+        <f t="shared" ref="S88:X88" si="205">+S86-S87</f>
         <v>-19.968999999999994</v>
       </c>
       <c r="T88" s="16">
-        <f t="shared" si="203"/>
+        <f t="shared" si="205"/>
         <v>27.784999999999997</v>
       </c>
       <c r="U88" s="16">
-        <f t="shared" si="203"/>
+        <f t="shared" si="205"/>
         <v>-8.0679999999999872</v>
       </c>
       <c r="V88" s="16">
-        <f t="shared" si="203"/>
+        <f t="shared" si="205"/>
         <v>2.4759999999999955</v>
       </c>
       <c r="W88" s="16">
-        <f t="shared" si="203"/>
+        <f t="shared" si="205"/>
         <v>27.856999999999999</v>
       </c>
       <c r="X88" s="16">
-        <f t="shared" si="203"/>
+        <f t="shared" si="205"/>
         <v>32.478000000000009</v>
       </c>
       <c r="Y88" s="16">
@@ -19682,12 +19683,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100764A4B226BE2F34C80DFAA3D37A3CB30" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="70544b0716d1f2dd0e24adda29a3d132">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b05d82d297216baf5b26c55225140df">
     <xsd:element name="properties">
@@ -19801,6 +19796,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -19811,15 +19812,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0F9EAB-5E81-4AEB-8A08-E4BC93860984}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99CC71A0-7761-4437-B521-535AC9386643}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19835,6 +19827,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0F9EAB-5E81-4AEB-8A08-E4BC93860984}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BD66871-8C69-48C0-A2A5-033DCAC1EF10}">
   <ds:schemaRefs>
